--- a/data/lstm ready data/mta_mapping_bemerkung.xlsx
+++ b/data/lstm ready data/mta_mapping_bemerkung.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C457"/>
+  <dimension ref="A1:C449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,177 +553,177 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anlage in not-aus ohne störung. robtech informiert</t>
+          <t>anlage leer , auffüllen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>anlage in not-aus ohne störung. robtech informiert</t>
+          <t>anlage leer , auffüllen</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>anlage leer , auffüllen</t>
+          <t>anlage leer ,auffüllen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>anlage leer , auffüllen</t>
+          <t>anlage leer ,auffüllen</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anlage leer ,auffüllen</t>
+          <t>anlage leer durch störungen, auffüllen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>anlage leer ,auffüllen</t>
+          <t>anlage leer durch störungen, auffüllen</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anlage leer durch störungen, auffüllen</t>
+          <t>anlage leer fahren</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>anlage leer durch störungen, auffüllen</t>
+          <t>anlage leer fahren</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anlage leer fahren</t>
+          <t>anlage leer gefahren</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>anlage leer fahren</t>
+          <t>anlage leer gefahren</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anlage leer gefahren</t>
+          <t>anlage leer gefahren ,auffüllen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>anlage leer gefahren</t>
+          <t>anlage leer gefahren ,auffüllen</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>anlage leer gefahren ,auffüllen</t>
+          <t>anlage leer gefahren wegen störung</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>anlage leer gefahren ,auffüllen</t>
+          <t>anlage leer gefahren wegen störung</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>anlage leer gefahren wegen störung</t>
+          <t>anlage leer gelaufen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>anlage leer gefahren wegen störung</t>
+          <t>anlage leer gelaufen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>anlage leer gelaufen</t>
+          <t>anlage leer gelaufen, auffüllen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>anlage leer gelaufen</t>
+          <t>anlage leer gelaufen, auffüllen</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>anlage leer gelaufen auffüllen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>anlage leer gelaufen, auffüllen</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>anlage leer gelaufen, auffüllen</t>
-        </is>
-      </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>anlage leer gelaufen auffüllen</t>
+          <t>anlage leer übernomen, auffüllen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>anlage leer gelaufen, auffüllen</t>
+          <t>anlage leer übernomen, auffüllen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>anlage leer übernomen, auffüllen</t>
+          <t>anlage leer übernomen,auffüllen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>anlage leer übernomen, auffüllen</t>
+          <t>anlage leer übernomen,auffüllen</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -733,222 +733,222 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>anlage leer übernomen,auffüllen</t>
+          <t>anlage leer, auffüllen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>anlage leer übernomen,auffüllen</t>
+          <t>anlage leer, auffüllen</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>anlage leer auffüllen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>anlage leer, auffüllen</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>anlage leer, auffüllen</t>
-        </is>
-      </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>anlage leer auffüllen</t>
+          <t>anlage nach stromausfall durch robotertechniker anstellen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>anlage leer, auffüllen</t>
+          <t>anlage nach stromausfall durch robotertechniker anstellen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>anlage nach stromausfall durch robotertechniker anstellen</t>
+          <t>anlage nach störungen leer, auffüllen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>anlage nach stromausfall durch robotertechniker anstellen</t>
+          <t>anlage nach störungen leer, auffüllen</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>anlage nach störungen leer, auffüllen</t>
+          <t>anlage reinigung und wartung</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>anlage nach störungen leer, auffüllen</t>
+          <t>anlage reinigung und wartung</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>anlage reinigung und wartung</t>
+          <t>anlage störung kein shtrom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>anlage reinigung und wartung</t>
+          <t>anlage störung kein shtrom</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>anlage störung kein shtrom</t>
+          <t>anlage störung nach stromausfall. robotech an der anlage.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>anlage störung kein shtrom</t>
+          <t>anlage störung nach stromausfall. robotech an der anlage.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>anlage störung nach stromausfall. robotech an der anlage.</t>
+          <t>anlage voll</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>anlage störung nach stromausfall. robotech an der anlage.</t>
+          <t>anlage voll</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>anlage voll</t>
+          <t>anlage voll fahren</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>anlage voll</t>
+          <t>anlage voll fahren</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>anlge voll fahren</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>anlage voll fahren</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>anlage voll fahren</t>
-        </is>
-      </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>anlge voll fahren</t>
+          <t>aufräumen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>anlage voll fahren</t>
+          <t>aufräumen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aufräumen,werkzeug wegpacken</t>
+          <t>auftag aus anlage räumen, robtech wegen folge störung angerufen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aufräumen,werkzeug wegpacken</t>
+          <t>auftag aus anlage räumen, robtech wegen folge störung angerufen</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>auftag aus anlage räumen, robtech wegen folge störung angerufen</t>
+          <t>batterien der fernbedienung vom kran leer, elektriker informiert</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>auftag aus anlage räumen, robtech wegen folge störung angerufen</t>
+          <t>batterien der fernbedienung vom kran leer, elektriker informiert</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>batterien der fernbedienung vom kran leer, elektriker informiert</t>
+          <t>bauteilspanner spannen nicht</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>batterien der fernbedienung vom kran leer, elektriker informiert</t>
+          <t>bauteilspanner spannen nicht</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bauteilspanner spannen nicht</t>
+          <t>bedienerschtz wird ausgelöst obwohl stw vorhanden ist (robtech informiert)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bauteilspanner spannen nicht</t>
+          <t>bedienerschtz wird ausgelöst obwohl stw vorhanden ist (robtech informiert)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -958,46 +958,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bedienerschtz wird ausgelöst obwohl stw vorhanden ist (robtech informiert)</t>
+          <t>bedienerschutz ausgelöst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bedienerschtz wird ausgelöst obwohl stw vorhanden ist (robtech informiert)</t>
+          <t>bedienerschutz ausgelöst</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>bedienerschtz ausgelöst</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>bedienerschutz ausgelöst</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>bedienerschutz ausgelöst</t>
-        </is>
-      </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bedienerschtz ausgelöst</t>
+          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst</t>
+          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1008,172 +1008,172 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst + folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst ohne das jemand ihn ausgelöst hat ( mehrfach ) folgestörungen behoben</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst + folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst ohne das jemand ihn ausgelöst hat ( mehrfach ) folgestörungen behoben</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst ohne das jemand ihn ausgelöst hat ( mehrfach ) folgestörungen behoben</t>
+          <t>bedienerschutz ausgelöst und folgefehler beheben</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst ohne das jemand ihn ausgelöst hat ( mehrfach ) folgestörungen behoben</t>
+          <t>bedienerschutz ausgelöst und folgefehler beheben</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst und folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst, folgefehler beheben</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst und folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst, folgefehler beheben</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst, folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst, folgestörungen beheben</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst, folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst, folgestörungen beheben</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>bedienerschutz ausgelöst, folgestörungen behoben</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>bedienerschutz ausgelöst, folgestörungen beheben</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>bedienerschutz ausgelöst, folgestörungen beheben</t>
-        </is>
-      </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst, folgestörungen behoben</t>
+          <t>beim knoten schweißen festgefahren</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst, folgestörungen beheben</t>
+          <t>beim knoten schweißen festgefahren</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>beim knoten schweißen festgefahren</t>
+          <t>betriebsversammlung</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>beim knoten schweißen festgefahren</t>
+          <t>betriebsversammlung</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>betriebsversammlung</t>
+          <t>bleibt beim schweißen ohne grund stehen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>betriebsversammlung</t>
+          <t>bleibt beim schweißen ohne grund stehen</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bleibt beim schweißen ohne grund stehen</t>
+          <t>brenner gewechselt</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>bleibt beim schweißen ohne grund stehen</t>
+          <t>brenner gewechselt</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>brenner gewechselt</t>
+          <t>brenner gewechselt und robtech informiert zwecks störungsbehebung</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>brenner gewechselt</t>
+          <t>brenner gewechselt und robtech informiert zwecks störungsbehebung</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>brenner gewechselt und robtech informiert zwecks störungsbehebung</t>
+          <t>brenner prüfen durch robtech</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>brenner gewechselt und robtech informiert zwecks störungsbehebung</t>
+          <t>brenner prüfen durch robtech</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1183,42 +1183,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>brenner prüfen durch robtech</t>
+          <t>brenner prüfen durch robtech und drahtsehne erneuern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>brenner prüfen durch robtech</t>
+          <t>brenner prüfen durch robtech und drahtsehne erneuern</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>brenner prüfen durch robtech und drahtsehne erneuern</t>
+          <t>brenner prüfen lassen durch robtech</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>brenner prüfen durch robtech und drahtsehne erneuern</t>
+          <t>brenner prüfen lassen durch robtech</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>brenner prüfen lassen durch robtech</t>
+          <t>brenner prüfen, robetech informiert</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>brenner prüfen lassen durch robtech</t>
+          <t>brenner prüfen, robetech informiert</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1228,27 +1228,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>brenner prüfen, robetech informiert</t>
+          <t>brenner richten durch robtech</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>brenner prüfen, robetech informiert</t>
+          <t>brenner richten durch robtech</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>brenner richten durch robtech</t>
+          <t>brenner richten lassen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>brenner richten durch robtech</t>
+          <t>brenner richten lassen</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1258,42 +1258,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>brenner richten lassen</t>
+          <t>brenner tauschen, zwecks mehrfacher leonie störungen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>brenner richten lassen</t>
+          <t>brenner tauschen, zwecks mehrfacher leonie störungen</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>brenner tauschen, zwecks mehrfacher leonie störungen</t>
+          <t>brenner und düse wurde gewechselt</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>brenner tauschen, zwecks mehrfacher leonie störungen</t>
+          <t>brenner und düse wurde gewechselt</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>brenner und düse wurde gewechselt</t>
+          <t>brenner wechseln</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>brenner und düse wurde gewechselt</t>
+          <t>brenner wechseln</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1303,12 +1303,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>brenner wechseln</t>
+          <t>brenner, nach kollission ohne meldung richten lassen. pos. stirnwand passt nicht</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>brenner wechseln</t>
+          <t>brenner, nach kollission ohne meldung richten lassen. pos. stirnwand passt nicht</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1318,42 +1318,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>brenner, nach kollission ohne meldung richten lassen. pos. stirnwand passt nicht</t>
+          <t>brennerkollision</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>brenner, nach kollission ohne meldung richten lassen. pos. stirnwand passt nicht</t>
+          <t>brennerkollision</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>brennerkollision</t>
+          <t>daten nicht verfügbar</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>brennerkollision</t>
+          <t>daten nicht verfügbar</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>daten nicht verfügbar</t>
+          <t>daten verlust</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>daten nicht verfügbar</t>
+          <t>daten verlust</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1363,67 +1363,67 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>daten verlust</t>
+          <t>draht gewechselt</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>daten verlust</t>
+          <t>draht gewechselt</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>draht gewechselt</t>
+          <t>drahtfass gewechselt</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>draht gewechselt</t>
+          <t>drahtfass gewechselt</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>drahtfass gewechselt</t>
+          <t>drahtfass wechseln</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>drahtfass gewechselt</t>
+          <t>drahtfass wechseln</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>drahtfasswechseln</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>drahtfass wechseln</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>drahtfass wechseln</t>
-        </is>
-      </c>
       <c r="C66" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>drahtfasswechseln</t>
+          <t>drahtfass wechsel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,78 +1432,78 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>drahtfass wechsel</t>
+          <t>drahtfasswechsel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>drahtfass wechseln</t>
+          <t>drahtfasswechsel</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>drahtfasswechsel</t>
+          <t>drahtfasswechsel ( hit welding industry )</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>drahtfasswechsel</t>
+          <t>drahtfasswechsel ( hit welding industry )</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>drahtfasswechsel ( hit welding industry )</t>
+          <t>drahtfasswechsel ( hit welding industry drahtfass )</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>drahtfasswechsel ( hit welding industry )</t>
+          <t>drahtfasswechsel ( hit welding industry drahtfass )</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>drahtfasswechsel ( hit welding industry drahtfass )</t>
+          <t>drahtfasswechsel + drahtsehne gewechselt</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>drahtfasswechsel ( hit welding industry drahtfass )</t>
+          <t>drahtfasswechsel + drahtsehne gewechselt</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>drahtfasswechsel + drahtsehne gewechselt</t>
+          <t>drahtfasswechsel,</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>drahtfasswechsel + drahtsehne gewechselt</t>
+          <t>drahtfasswechsel,</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1513,12 +1513,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>drahtfasswechsel,</t>
+          <t>drahtfaß wechseln</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>drahtfasswechsel,</t>
+          <t>drahtfaß wechseln</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1528,12 +1528,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>drahtfaß wechseln</t>
+          <t>drahtfaß wechseln (test )</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>drahtfaß wechseln</t>
+          <t>drahtfaß wechseln (test )</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1543,12 +1543,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>drahtfaß wechseln (test )</t>
+          <t>drahtförderschlauch an banane abgerissen, draht hat irgendwoher masse bekommen und ist von der banane bis in den brennerkopf durchgeschmohrt, robtech informiert</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>drahtfaß wechseln (test )</t>
+          <t>drahtförderschlauch an banane abgerissen, draht hat irgendwoher masse bekommen und ist von der banane bis in den brennerkopf durchgeschmohrt, robtech informiert</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1558,12 +1558,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>drahtförderschlauch an banane abgerissen, draht hat irgendwoher masse bekommen und ist von der banane bis in den brennerkopf durchgeschmohrt, robtech informiert</t>
+          <t>drahtförderschlauch von fronius zur banane abgerissen, robtech informiert</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>drahtförderschlauch an banane abgerissen, draht hat irgendwoher masse bekommen und ist von der banane bis in den brennerkopf durchgeschmohrt, robtech informiert</t>
+          <t>drahtförderschlauch von fronius zur banane abgerissen, robtech informiert</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1573,12 +1573,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>drahtförderschlauch von fronius zur banane abgerissen, robtech informiert</t>
+          <t>drahtrolle tauschen.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>drahtförderschlauch von fronius zur banane abgerissen, robtech informiert</t>
+          <t>drahtrolle tauschen.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1588,12 +1588,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>drahtrolle tauschen.</t>
+          <t>drahtsehne im brenner erneuert</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>drahtrolle tauschen.</t>
+          <t>drahtsehne im brenner erneuert</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1603,12 +1603,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>drahtsehne im brenner erneuert</t>
+          <t>drahtwechseln</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>drahtsehne im brenner erneuert</t>
+          <t>drahtwechseln</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1618,72 +1618,72 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>drahtwechseln</t>
+          <t>drahtwechseln,</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>drahtwechseln</t>
+          <t>drahtwechseln,</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>drahtwechseln,</t>
+          <t>dratfasswechsel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>drahtwechseln,</t>
+          <t>dratfasswechsel</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dratfasswechsel</t>
+          <t>drucker funktoniert nicht ( gestelle steht vorne beim tor)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>dratfasswechsel</t>
+          <t>drucker funktoniert nicht ( gestelle steht vorne beim tor)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>drucker funktoniert nicht ( gestelle steht vorne beim tor)</t>
+          <t>eckrung loch nachboren -wb.63</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>drucker funktoniert nicht ( gestelle steht vorne beim tor)</t>
+          <t>eckrung loch nachboren -wb.63</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>eckrung loch nachboren -wb.63</t>
+          <t>eckrungen durch eckrungenanlage nachgearbeitet</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eckrung loch nachboren -wb.63</t>
+          <t>eckrungen durch eckrungenanlage nachgearbeitet</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1693,42 +1693,42 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>eckrungen durch eckrungenanlage nachgearbeitet</t>
+          <t>elektriker wegen kran störung vor ort, an kranvorrichtung</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>eckrungen durch eckrungenanlage nachgearbeitet</t>
+          <t>elektriker wegen kran störung vor ort, an kranvorrichtung</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>elektriker wegen kran störung vor ort, an kranvorrichtung</t>
+          <t>endabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>elektriker wegen kran störung vor ort, an kranvorrichtung</t>
+          <t>endabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>endabschalter a6 störung, robtech informiert</t>
+          <t>f h1 sicherung op 90/100/110 haben kein strom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>endabschalter a6 störung, robtech informiert</t>
+          <t>f h1 sicherung op 90/100/110 haben kein strom</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1738,42 +1738,42 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>f h1 sicherung op 90/100/110 haben kein strom</t>
+          <t>falsche bleche auf dem tb gestell (bleche raustragen aus der anlage )</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>f h1 sicherung op 90/100/110 haben kein strom</t>
+          <t>falsche bleche auf dem tb gestell (bleche raustragen aus der anlage )</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>falsche bleche auf dem tb gestell (bleche raustragen aus der anlage )</t>
+          <t>falsches blech (soll 797 l5 ist aber l4 )</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>falsche bleche auf dem tb gestell (bleche raustragen aus der anlage )</t>
+          <t>falsches blech (soll 797 l5 ist aber l4 )</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>falsches blech (soll 797 l5 ist aber l4 )</t>
+          <t>feder und sauger tauschen (robtech vor ort)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>falsches blech (soll 797 l5 ist aber l4 )</t>
+          <t>feder und sauger tauschen (robtech vor ort)</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1783,42 +1783,42 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>feder und sauger tauschen (robtech vor ort)</t>
+          <t>fehler schritkette robotech informiert.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>feder und sauger tauschen (robtech vor ort)</t>
+          <t>fehler schritkette robotech informiert.</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fehler schritkette robotech informiert.</t>
+          <t>fehler schrittkette ( robotech informiert )</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fehler schritkette robotech informiert.</t>
+          <t>fehler schrittkette ( robotech informiert )</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fehler schrittkette ( robotech informiert )</t>
+          <t>fehler: festo linearantrieb robotech an der anlage.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fehler schrittkette ( robotech informiert )</t>
+          <t>fehler: festo linearantrieb robotech an der anlage.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1828,87 +1828,87 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>fehler: festo linearantrieb robotech an der anlage.</t>
+          <t>fehler: festo linearantrieb robotech informiert.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fehler: festo linearantrieb robotech an der anlage.</t>
+          <t>fehler: festo linearantrieb robotech informiert.</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>fehler: festo linearantrieb robotech informiert.</t>
+          <t>festgebrannt</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fehler: festo linearantrieb robotech informiert.</t>
+          <t>festgebrannt</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>festgebrannt</t>
+          <t>festgefahren</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>festgebrannt</t>
+          <t>festgefahren</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>festgefahren</t>
+          <t>festo linearbestrieb störung, robtech informiert</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>festgefahren</t>
+          <t>festo linearbestrieb störung, robtech informiert</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>festo linearbestrieb störung, robtech informiert</t>
+          <t>fronius fehler</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>festo linearbestrieb störung, robtech informiert</t>
+          <t>fronius fehler</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>fronius fehler</t>
+          <t>froniussensor prüfen, durch robtech</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fronius fehler</t>
+          <t>froniussensor prüfen, durch robtech</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1918,42 +1918,42 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>froniussensor prüfen, durch robtech</t>
+          <t>gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>froniussensor prüfen, durch robtech</t>
+          <t>gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>kontaktrohr und gasdüse gewechselt</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>gasdüse und kontaktrohr gewechselt</t>
-        </is>
-      </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kontaktrohr und gasdüse gewechselt</t>
+          <t>gravierer störung, robtech an der anlage</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>gasdüse und kontaktrohr gewechselt</t>
+          <t>gravierer störung, robtech an der anlage</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1963,57 +1963,57 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gravierer störung, robtech an der anlage</t>
+          <t>greifer störung beim abholen des 2. bleches in op 25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>gravierer störung, robtech an der anlage</t>
+          <t>greifer störung beim abholen des 2. bleches in op 25</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>greifer störung beim abholen des 2. bleches in op 25</t>
+          <t>hinterer spanner schließt ab und zu nicht, beim abholen vom 2. blech in op 25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>greifer störung beim abholen des 2. bleches in op 25</t>
+          <t>hinterer spanner schließt ab und zu nicht, beim abholen vom 2. blech in op 25</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>hinterer spanner schließt ab und zu nicht, beim abholen vom 2. blech in op 25</t>
+          <t>hubtor sensor defekt (robtech informiert)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>hinterer spanner schließt ab und zu nicht, beim abholen vom 2. blech in op 25</t>
+          <t>hubtor sensor defekt (robtech informiert)</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hubtor sensor defekt (robtech informiert)</t>
+          <t>höhe von querträger oben angepasst.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hubtor sensor defekt (robtech informiert)</t>
+          <t>höhe von querträger oben angepasst.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2023,12 +2023,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>höhe von querträger oben angepasst.</t>
+          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>höhe von querträger oben angepasst.</t>
+          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2038,27 +2038,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>in op.120-1 schweißnahtqualität schlecht qt. unten nachschweißen</t>
+          <t>kein bediener, reinigung</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>in op.120-1 schweißnahtqualität schlecht qt. unten nachschweißen</t>
+          <t>kein bediener, reinigung</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
+          <t>kein gas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
+          <t>kein gas</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2068,72 +2068,72 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kein bediener, reinigung</t>
+          <t>kein gas mehr, durch robtech informiert</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kein bediener, reinigung</t>
+          <t>kein gas mehr, durch robtech informiert</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kein gas</t>
+          <t>kein monteur</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kein gas</t>
+          <t>kein monteur</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kein gas mehr, durch robtech informiert</t>
+          <t>kein montuer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kein gas mehr, durch robtech informiert</t>
+          <t>kein montuer</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kein monteur</t>
+          <t>kein vakuum</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kein monteur</t>
+          <t>kein vakuum</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kein montuer</t>
+          <t>kein vakuum bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kein montuer</t>
+          <t>kein vakuum bleche kleben aneinander</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2143,117 +2143,117 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kein vakuum</t>
+          <t>kein vakuum, bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>kein vakuum</t>
+          <t>kein vakuum bleche kleben aneinander</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kein vakuum bleche kleben aneinander</t>
+          <t>keine daten robotech an der anlage</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kein vakuum bleche kleben aneinander</t>
+          <t>keine daten robotech an der anlage</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kein vakuum, bleche kleben aneinander</t>
+          <t>keine l-5 füsse für stüzen.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kein vakuum bleche kleben aneinander</t>
+          <t>keine l-5 füsse für stüzen.</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>keine daten robotech an der anlage</t>
+          <t>keine mes- daten</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>keine daten robotech an der anlage</t>
+          <t>keine mes- daten</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>keine l-5 füsse für stüzen.</t>
+          <t>knoten 3 klemmt (robotech informiert)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>keine l-5 füsse für stüzen.</t>
+          <t>knoten 3 klemmt (robotech informiert)</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>keine mes- daten</t>
+          <t>knoten 3 klemmt in op 50</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>keine mes- daten</t>
+          <t>knoten 3 klemmt in op 50</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt (robotech informiert)</t>
+          <t>knotengreifer 3 störung beim abholen in op 70</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt (robotech informiert)</t>
+          <t>knotengreifer 3 störung beim abholen in op 70</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt in op 50</t>
+          <t>knotenschweißgerät defekt elektriker informiert</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt in op 50</t>
+          <t>knotenschweißgerät defekt elektriker informiert</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2263,27 +2263,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>knotengreifer 3 störung beim abholen in op 70</t>
+          <t>kollision</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>knotengreifer 3 störung beim abholen in op 70</t>
+          <t>kollision</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>knotenschweißgerät defekt elektriker informiert</t>
+          <t>kollision ( robotech informiert)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>knotenschweißgerät defekt elektriker informiert</t>
+          <t>kollision ( robotech informiert)</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2293,27 +2293,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kollision</t>
+          <t>kollision (brenner prüfen durch robotech.)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kollision</t>
+          <t>kollision (brenner prüfen durch robotech.)</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kollision ( robotech informiert)</t>
+          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>kollision ( robotech informiert)</t>
+          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2323,27 +2323,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kollision (brenner prüfen durch robotech.)</t>
+          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kollision (brenner prüfen durch robotech.)</t>
+          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
+          <t>kollision mit stw l4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
+          <t>kollision mit stw l4</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2353,42 +2353,42 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
+          <t>kollisionsabfrage</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
+          <t>kollisionsabfrage</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kollision mit stw l4</t>
+          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>kollision mit stw l4</t>
+          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kollisionsabfrage</t>
+          <t>kran defekt (elektriker an de anlage.)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kollisionsabfrage</t>
+          <t>kran defekt (elektriker an de anlage.)</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2398,27 +2398,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
+          <t>kran fernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
+          <t>kran fernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kran defekt (elektriker an de anlage.)</t>
+          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kran defekt (elektriker an de anlage.)</t>
+          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2428,12 +2428,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kran fernbedienung defekt, elektriker informiert</t>
+          <t>kran störung, elektriker informiert</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>kran fernbedienung defekt, elektriker informiert</t>
+          <t>kran störung, elektriker informiert</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2443,12 +2443,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
+          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
+          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2458,12 +2458,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kran störung, elektriker informiert</t>
+          <t>kranfernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kran störung, elektriker informiert</t>
+          <t>kranfernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2473,252 +2473,252 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
+          <t>kratzer in der stirnwand ausbessern.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
+          <t>kratzer in der stirnwand ausbessern.</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kranfernbedienung defekt, elektriker informiert</t>
+          <t>kratzer in stw nacharbeiten</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kranfernbedienung defekt, elektriker informiert</t>
+          <t>kratzer in stw nacharbeiten</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kratzer in der stirnwand ausbessern.</t>
+          <t>l5 muttern organisieren</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kratzer in der stirnwand ausbessern.</t>
+          <t>l5 muttern organisieren</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kratzer in stw nacharbeiten</t>
+          <t>laser störung</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kratzer in stw nacharbeiten</t>
+          <t>laser störung</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>l5 muttern organisieren</t>
+          <t>laserscanner messwerte störung, robtech informiert</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>l5 muttern organisieren</t>
+          <t>laserscanner messwerte störung, robtech informiert</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>laser störung</t>
+          <t>leoni störung</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>laser störung</t>
+          <t>leoni störung</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>laserscanner messwerte störung, robtech informiert</t>
+          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>laserscanner messwerte störung, robtech informiert</t>
+          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>leoni störung</t>
+          <t>leonie fahrt störung</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>leoni störung</t>
+          <t>leonie fahrt störung</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
+          <t>leonie störung</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
+          <t>leonie störung</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>leonie fahrt störung</t>
+          <t>leonie störung robotech in der anlage</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>leonie fahrt störung</t>
+          <t>leonie störung robotech in der anlage</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>leonie störung</t>
+          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>leonie störung</t>
+          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>leonie störung robotech in der anlage</t>
+          <t>leonie störungen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>leonie störung robotech in der anlage</t>
+          <t>leonie störungen</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
+          <t>leonifehler ohne fehlermeldung.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
+          <t>leonifehler ohne fehlermeldung.</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>leonie störungen</t>
+          <t>leonifehler, robtech informiert,warten auf robtech</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>leonie störungen</t>
+          <t>leonifehler, robtech informiert,warten auf robtech</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>leonifehler ohne fehlermeldung.</t>
+          <t>leonifehler.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>leonifehler ohne fehlermeldung.</t>
+          <t>leonifehler.</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>leonifehler, robtech informiert,warten auf robtech</t>
+          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>leonifehler, robtech informiert,warten auf robtech</t>
+          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2728,42 +2728,42 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
+          <t>liner 4 einseitig.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
+          <t>liner 4 einseitig.</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
+          <t>maschine leer gefahren</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
+          <t>maschine leer gefahren</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>liner 4 einseitig.</t>
+          <t>mehraufwand nacharbeiten</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>liner 4 einseitig.</t>
+          <t>mehraufwand nacharbeiten</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2773,27 +2773,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>maschine leer gefahren</t>
+          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>maschine leer gefahren</t>
+          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>mehraufwand nacharbeiten</t>
+          <t>mehraufwand nachschweißen . ( qt oben )</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>mehraufwand nacharbeiten</t>
+          <t>mehraufwand nachschweißen . ( qt oben )</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2803,27 +2803,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
+          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
+          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( qt oben )</t>
+          <t>mehraufwand nachschweißen . ( stuetze .)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( qt oben )</t>
+          <t>mehraufwand nachschweißen . ( stuetze .)</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2833,27 +2833,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
+          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
+          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze .)</t>
+          <t>mes daten störung</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze .)</t>
+          <t>mes daten störung</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2863,42 +2863,42 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
+          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
+          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>mes daten störung</t>
+          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>mes daten störung</t>
+          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
+          <t>messwerte laser n.i.o (robotech informiert)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
+          <t>messwerte laser n.i.o (robotech informiert)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2908,27 +2908,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
+          <t>mitarbeiterpause aufgrund der temperaturen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
+          <t>mitarbeiterpause aufgrund der temperaturen</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>messwerte laser n.i.o (robotech informiert)</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>messwerte laser n.i.o (robotech informiert)</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2938,12 +2938,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>mitarbeiterpause aufgrund der temperaturen</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>mitarbeiterpause aufgrund der temperaturen</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2953,12 +2953,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
+          <t>monatliche wartungsplan</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
+          <t>monatliche wartungsplan</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2968,12 +2968,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
+          <t>nacharbeitszellen kein strom, elektriker informiert</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
+          <t>nacharbeitszellen kein strom, elektriker informiert</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2983,12 +2983,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>monatliche wartungsplan</t>
+          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>monatliche wartungsplan</t>
+          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2998,12 +2998,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nacharbeitszellen kein strom, elektriker informiert</t>
+          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nacharbeitszellen kein strom, elektriker informiert</t>
+          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3013,27 +3013,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
+          <t>niecht activ nur op.130-2. so übernomen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
+          <t>niecht activ nur op.130-2. so übernomen</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
+          <t>not halt störung und folge fehler beheben</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
+          <t>not halt störung und folge fehler beheben</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3043,42 +3043,42 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>niecht activ nur op.130-2. so übernomen</t>
+          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>niecht activ nur op.130-2. so übernomen</t>
+          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>not halt störung und folge fehler beheben</t>
+          <t>nur 1 schweißer an der anlage</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>not halt störung und folge fehler beheben</t>
+          <t>nur 1 schweißer an der anlage</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
+          <t>nur ein schweißer an der anlage</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
+          <t>nur ein schweißer an der anlage</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3088,102 +3088,102 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>nur 1 schweißer an der anlage</t>
+          <t>nur op-130-1. ist aktiv</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>nur 1 schweißer an der anlage</t>
+          <t>nur op-130-1. ist aktiv</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>nur ein schweißer an der anlage</t>
+          <t>op passiv geschaltet</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>nur ein schweißer an der anlage</t>
+          <t>op passiv geschaltet</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>nur op-130-1. ist aktiv</t>
+          <t>op passiv geschaltet l-4</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>nur op-130-1. ist aktiv</t>
+          <t>op passiv geschaltet l-4</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>op passiv geschaltet</t>
+          <t>op passiv geschaltet l-5</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>op passiv geschaltet</t>
+          <t>op passiv geschaltet l-5</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-4</t>
+          <t>op.100-op110.- mehraufwand nachschweißen .</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-4</t>
+          <t>op.100-op110.- mehraufwand nachschweißen .</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-5</t>
+          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-5</t>
+          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen .</t>
+          <t>op.50 problem mit schrittkette robotech informiert.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen .</t>
+          <t>op.50 problem mit schrittkette robotech informiert.</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3193,27 +3193,27 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
+          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
+          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>op.50 problem mit schrittkette robotech informiert.</t>
+          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>op.50 problem mit schrittkette robotech informiert.</t>
+          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3223,12 +3223,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
+          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
+          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3238,12 +3238,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
+          <t>op50 vakuum störung</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
+          <t>op50 vakuum störung</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3253,12 +3253,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
+          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
+          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3268,12 +3268,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>op50 vakuum störung</t>
+          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>op50 vakuum störung</t>
+          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3283,27 +3283,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
+          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
+          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>parkposition passt nicht. m4 springt auf ref.</t>
+          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>parkposition passt nicht. m4 springt auf ref.</t>
+          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3313,12 +3313,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
+          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
+          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3328,42 +3328,42 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
+          <t>probleme mit dem laser .(robotech informiert</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
+          <t>probleme mit dem laser .(robotech informiert</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
+          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
+          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
+          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
+          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3373,12 +3373,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>probleme mit dem laser .(robotech informiert</t>
+          <t>probleme mit gravierer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>probleme mit dem laser .(robotech informiert</t>
+          <t>probleme mit gravierer</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3388,12 +3388,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
+          <t>probleme mit kontaktrohr</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
+          <t>probleme mit kontaktrohr</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3403,12 +3403,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
+          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
+          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3418,12 +3418,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>probleme mit gravierer</t>
+          <t>probleme mit kran- funkstörung</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>probleme mit gravierer</t>
+          <t>probleme mit kran- funkstörung</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3433,57 +3433,57 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr</t>
+          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr</t>
+          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
+          <t>probleme mit r 03 &amp; r 07 leoni</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
+          <t>probleme mit r 03 &amp; r 07 leoni</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>probleme mit kran- funkstörung</t>
+          <t>probleme mit schweißdraht</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>probleme mit kran- funkstörung</t>
+          <t>probleme mit schweißdraht</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
+          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
+          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3493,42 +3493,42 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>probleme mit r 03 &amp; r 07 leoni</t>
+          <t>probleme mit schweißdraht (robotech informiert)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>probleme mit r 03 &amp; r 07 leoni</t>
+          <t>probleme mit schweißdraht (robotech informiert)</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht</t>
+          <t>probleme mit schweißdraht .robotech .an der anlage</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht</t>
+          <t>probleme mit schweißdraht .robotech .an der anlage</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
+          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
+          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3538,57 +3538,57 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht (robotech informiert)</t>
+          <t>probleme mit sensor am tor (robotech infor)</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht (robotech informiert)</t>
+          <t>probleme mit sensor am tor (robotech infor)</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht .robotech .an der anlage</t>
+          <t>probleme mit stromdüse</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht .robotech .an der anlage</t>
+          <t>probleme mit stromdüse</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
+          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
+          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>probleme mit sensor am tor (robotech infor)</t>
+          <t>probleme mit stromdüse ( tauschen.)</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>probleme mit sensor am tor (robotech infor)</t>
+          <t>probleme mit stromdüse ( tauschen.)</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3598,42 +3598,42 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse</t>
+          <t>programm fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse</t>
+          <t>programm fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
+          <t>programm störung, robtech informiert</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
+          <t>programm störung, robtech informiert</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( tauschen.)</t>
+          <t>programm verlust (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( tauschen.)</t>
+          <t>programm verlust (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3643,27 +3643,27 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>programm fehler (robtech an der anlage)</t>
+          <t>programmtörung von r 05, robtech informiert</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>programm fehler (robtech an der anlage)</t>
+          <t>programmtörung von r 05, robtech informiert</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>programm störung, robtech informiert</t>
+          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>programm störung, robtech informiert</t>
+          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3673,12 +3673,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>programm verlust (robtech an der anlage)</t>
+          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>programm verlust (robtech an der anlage)</t>
+          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3688,12 +3688,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>programmtörung von r 05, robtech informiert</t>
+          <t>querträger für l5 fählt</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>programmtörung von r 05, robtech informiert</t>
+          <t>querträger für l5 fählt</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3703,12 +3703,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
+          <t>querträger oben einstellen durch robtech</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
+          <t>querträger oben einstellen durch robtech</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3718,12 +3718,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
+          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
+          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3733,12 +3733,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>querträger für l5 fählt</t>
+          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>querträger für l5 fählt</t>
+          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3748,12 +3748,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>querträger oben einstellen durch robtech</t>
+          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>querträger oben einstellen durch robtech</t>
+          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3763,12 +3763,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
+          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
+          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3778,12 +3778,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
+          <t>r 6 und r 7 kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
+          <t>r 6 und r 7 kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3793,12 +3793,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
+          <t>r.06 - probleme mit stromdüse</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
+          <t>r.06 - probleme mit stromdüse</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3808,12 +3808,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
+          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
+          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3823,12 +3823,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>r 05 sammelstörung op 50. sauger krumm, luftschlauchventil abgerissen</t>
+          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>r 05 sammelstörung op 50. sauger krumm, luftschlauchventil abgerissen</t>
+          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3838,12 +3838,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>r 6 und r 7 kontaktrohr gewechselt</t>
+          <t>reingung</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>r 6 und r 7 kontaktrohr gewechselt</t>
+          <t>reingung</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3853,147 +3853,147 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>r.06 - probleme mit stromdüse</t>
+          <t>reinigen</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>r.06 - probleme mit stromdüse</t>
+          <t>reinigen</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
+          <t>reinigen + werkzeug einschließen</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
+          <t>reinigen + werkzeug einschließen</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
+          <t>reinigen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
+          <t>reinigen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>reingung</t>
+          <t>reinigung</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>reingung</t>
+          <t>reinigung</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>527</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>reinigen</t>
+          <t>reinigung + werkzeug einschließen</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>reinigen</t>
+          <t>reinigung + werkzeug einschließen</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>203</v>
+        <v>88</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>reinigen + werkzeug einschließen</t>
+          <t>reinigung von außen</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>reinigen + werkzeug einschließen</t>
+          <t>reinigung von außen</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>reinigen,werkzeug wegpacken</t>
+          <t>reinigung.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>reinigen,werkzeug wegpacken</t>
+          <t>reinigung.</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>reinigung</t>
+          <t>robotech an der anlage neue bleche testen (186-190.)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>reinigung</t>
+          <t>robotech an der anlage neue bleche testen (186-190.)</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>538</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>reinigung + werkzeug einschließen</t>
+          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>reinigung + werkzeug einschließen</t>
+          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>reinigung von außen</t>
+          <t>robotechniker in der anlage</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>reinigung von außen</t>
+          <t>robotechniker in der anlage</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4003,87 +4003,87 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>reinigung.</t>
+          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>reinigung.</t>
+          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>robotech an der anlage neue bleche testen (186-190.)</t>
+          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>robotech an der anlage neue bleche testen (186-190.)</t>
+          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
+          <t>robtech an der anlage</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
+          <t>robtech an der anlage</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>robotechniker in der anlage</t>
+          <t>robtech bei der anlage</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>robotechniker in der anlage</t>
+          <t>robtech bei der anlage</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
+          <t>robtech informiert</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
+          <t>robtech informiert</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
+          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
+          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4093,27 +4093,27 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>robtech an der anlage</t>
+          <t>sauger beim abholen aus op 25 vakuum verloren</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>robtech an der anlage</t>
+          <t>sauger beim abholen aus op 25 vakuum verloren</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>robtech bei der anlage</t>
+          <t>sauger defekt</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>robtech bei der anlage</t>
+          <t>sauger defekt</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4123,42 +4123,42 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>robtech informiert</t>
+          <t>sauger defekt oder verdreht</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>robtech informiert</t>
+          <t>sauger defekt oder verdreht</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>robtech und schlosser vor ort</t>
+          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>robtech und schlosser vor ort</t>
+          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
+          <t>schrittketten fehler (anlage so übernommen)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
+          <t>schrittketten fehler (anlage so übernommen)</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4168,27 +4168,27 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>sauger beim abholen aus op 25 vakuum verloren</t>
+          <t>schrittketten fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>sauger beim abholen aus op 25 vakuum verloren</t>
+          <t>schrittketten fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>sauger defekt</t>
+          <t>schrittketten fehler und m1 antrieb fehler</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>sauger defekt</t>
+          <t>schrittketten fehler und m1 antrieb fehler</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4198,12 +4198,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>sauger defekt oder verdreht</t>
+          <t>schrittketten störung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>sauger defekt oder verdreht</t>
+          <t>schrittketten störung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4213,27 +4213,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
+          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
+          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>schrittketten fehler (anlage so übernommen)</t>
+          <t>schweißdraht festgebrannt</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>schrittketten fehler (anlage so übernommen)</t>
+          <t>schweißdraht festgebrannt</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4243,27 +4243,27 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>schrittketten fehler (robtech an der anlage)</t>
+          <t>schweißdraht wechseln</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>schrittketten fehler (robtech an der anlage)</t>
+          <t>schweißdraht wechseln</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>schrittketten fehler und m1 antrieb fehler</t>
+          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>schrittketten fehler und m1 antrieb fehler</t>
+          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4273,12 +4273,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>schrittketten störung (robtech an der anlage)</t>
+          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>schrittketten störung (robtech an der anlage)</t>
+          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4288,12 +4288,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
+          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
+          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4303,12 +4303,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>schweißdraht festgebrannt</t>
+          <t>schweißnahtqualität schlecht, robtech informiert</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>schweißdraht festgebrannt</t>
+          <t>schweißnahtqualität schlecht, robtech informiert</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4318,12 +4318,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>schweißdraht wechseln</t>
+          <t>schweißnähte nachtecachen</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>schweißdraht wechseln</t>
+          <t>schweißnähte nachtecachen</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4333,12 +4333,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
+          <t>schweißnähte schlecht, brenner tauschen</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
+          <t>schweißnähte schlecht, brenner tauschen</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4348,12 +4348,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
+          <t>schweißnähte teachen durch robtech</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
+          <t>schweißnähte teachen durch robtech</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4363,12 +4363,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
+          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
+          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4378,42 +4378,42 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht, robtech informiert</t>
+          <t>schweißstörung</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht, robtech informiert</t>
+          <t>schweißstörung</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>schweißnähte nachtecachen</t>
+          <t>schweißstörung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>schweißnähte nachtecachen</t>
+          <t>schweißstörung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>schweißnähte schlecht, brenner tauschen</t>
+          <t>schweißstörung .</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>schweißnähte schlecht, brenner tauschen</t>
+          <t>schweißstörung .</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4423,27 +4423,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>schweißnähte teachen durch robtech</t>
+          <t>schweißstörung am fronius</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>schweißnähte teachen durch robtech</t>
+          <t>schweißstörung am fronius</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
+          <t>schweißstörung am fronius in op.120-1</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
+          <t>schweißstörung am fronius in op.120-1</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4453,72 +4453,72 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>schweißstörung</t>
+          <t>schweißstörung am fronius robotech in der anlage</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>schweißstörung</t>
+          <t>schweißstörung am fronius robotech in der anlage</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>schweißstörung (robtech an der anlage)</t>
+          <t>schweißstörung bei op120.2</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>schweißstörung (robtech an der anlage)</t>
+          <t>schweißstörung bei op120.2</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>schweißstörung .</t>
+          <t>schweißstörung durch bauteil</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>schweißstörung .</t>
+          <t>schweißstörung durch bauteil</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius</t>
+          <t>schweißstörung in op-120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius</t>
+          <t>schweißstörung in op-120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius in op.120-1</t>
+          <t>schweißstörung in op.120-2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius in op.120-1</t>
+          <t>schweißstörung in op.120-2</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4528,27 +4528,27 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius robotech in der anlage</t>
+          <t>schweißstörung robotech informiert.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius robotech in der anlage</t>
+          <t>schweißstörung robotech informiert.</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>schweißstörung bei op120.2</t>
+          <t>schweißstörung.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>schweißstörung bei op120.2</t>
+          <t>schweißstörung.</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4558,27 +4558,27 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>schweißstörung durch bauteil</t>
+          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>schweißstörung durch bauteil</t>
+          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>schweißstörung in op-120.1 , robtech informiert</t>
+          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>schweißstörung in op-120.1 , robtech informiert</t>
+          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4588,12 +4588,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>schweißstörung in op.120-2</t>
+          <t>schwenkarm sensor links defekt, robtech informiert</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>schweißstörung in op.120-2</t>
+          <t>schwenkarm sensor links defekt, robtech informiert</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4603,12 +4603,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>schweißstörung robotech informiert.</t>
+          <t>sensor bauteilerkennung schaltet nicht</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>schweißstörung robotech informiert.</t>
+          <t>sensor bauteilerkennung schaltet nicht</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4618,27 +4618,27 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>schweißstörung.</t>
+          <t>sensor defekt robotech informiert</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>schweißstörung.</t>
+          <t>sensor defekt robotech informiert</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
+          <t>sew antrieb (robtech wurde informiert)</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
+          <t>sew antrieb (robtech wurde informiert)</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4648,12 +4648,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
+          <t>sew antrieb (stw stüße links eingeklemmt)</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
+          <t>sew antrieb (stw stüße links eingeklemmt)</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4663,12 +4663,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>schwenkarm sensor links defekt, robtech informiert</t>
+          <t>sew antrieb fehler - robtechnik informiert</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>schwenkarm sensor links defekt, robtech informiert</t>
+          <t>sew antrieb fehler - robtechnik informiert</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4678,12 +4678,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sensor bauteilerkennung schaltet nicht</t>
+          <t>sew antrieb m3</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>sensor bauteilerkennung schaltet nicht</t>
+          <t>sew antrieb m3</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4693,27 +4693,27 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sensor defekt robotech informiert</t>
+          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>sensor defekt robotech informiert</t>
+          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sew antrieb (robtech wurde informiert)</t>
+          <t>sew antriebs-störung</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>sew antrieb (robtech wurde informiert)</t>
+          <t>sew antriebs-störung</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4723,42 +4723,42 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sew antrieb (stw stüße links eingeklemmt)</t>
+          <t>sew antriebsstörung ( fehler 26 )</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>sew antrieb (stw stüße links eingeklemmt)</t>
+          <t>sew antriebsstörung ( fehler 26 )</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sew antrieb fehler - robtechnik informiert</t>
+          <t>sew antriebsstörung 26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>sew antrieb fehler - robtechnik informiert</t>
+          <t>sew antriebsstörung 26</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sew antrieb m3</t>
+          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>sew antrieb m3</t>
+          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4768,27 +4768,27 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sew antriebs-störung</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>sew antriebs-störung</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4798,27 +4798,27 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sew antriebsstörung ( fehler 26 )</t>
+          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>sew antriebsstörung ( fehler 26 )</t>
+          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>sew antriebsstörung 26</t>
+          <t>sew antriebsstörung, robtech informiert</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>sew antriebsstörung 26</t>
+          <t>sew antriebsstörung, robtech informiert</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4828,12 +4828,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
+          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
+          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4843,42 +4843,42 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
+          <t>softwareendabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
+          <t>softwareendabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
+          <t>softwarendabschaltungs störung bei op 120.1</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
+          <t>softwarendabschaltungs störung bei op 120.1</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
+          <t>softwereendschalter a6. ( robotech an der anlage )</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
+          <t>softwereendschalter a6. ( robotech an der anlage )</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4888,27 +4888,27 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sew antriebsstörung, robtech informiert</t>
+          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>sew antriebsstörung, robtech informiert</t>
+          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
+          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
+          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4918,87 +4918,87 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>softwareendabschalter a6 störung, robtech informiert</t>
+          <t>spanner klemmt.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>softwareendabschalter a6 störung, robtech informiert</t>
+          <t>spanner klemmt.</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>softwarendabschaltungs störung bei op 120.1</t>
+          <t>spanner richten (schlosser an der anlage)</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>softwarendabschaltungs störung bei op 120.1</t>
+          <t>spanner richten (schlosser an der anlage)</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>softwereendschalter a6. ( robotech an der anlage )</t>
+          <t>spanner störung, robtech informiert</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>softwereendschalter a6. ( robotech an der anlage )</t>
+          <t>spanner störung, robtech informiert</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
+          <t>spanner- knoten 1 spannen nicht in op.70</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
+          <t>spanner- knoten 1 spannen nicht in op.70</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
+          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
+          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>spanner klemmt.</t>
+          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>spanner klemmt.</t>
+          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5008,132 +5008,132 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>spanner richten (schlosser an der anlage)</t>
+          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>spanner richten (schlosser an der anlage)</t>
+          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>spanner störung, robtech informiert</t>
+          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>spanner störung, robtech informiert</t>
+          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht in op.70</t>
+          <t>stirnwand auf den böcken komplettiert</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht in op.70</t>
+          <t>stirnwand auf den böcken komplettiert</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
+          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
+          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
+          <t>stirnwand kompletiert</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
+          <t>stirnwand kompletiert</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
+          <t>stirnwand komplettiert</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
+          <t>stirnwand kompletiert</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
+          <t>stirnwand komplettieren</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
+          <t>stirnwand komplettieren</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken komplettiert</t>
+          <t>stirnwand nacharbeiten.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken komplettiert</t>
+          <t>stirnwand nacharbeiten.</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
+          <t>stirnwand nachgearbeitet und komplettiert</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
+          <t>stirnwand nachgearbeitet und komplettiert</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5143,72 +5143,72 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>stirnwand komplettieren</t>
+          <t>stirnwand von draußen komplettiert</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>stirnwand komplettieren</t>
+          <t>stirnwand von draußen komplettiert</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>stirnwand komplettiert</t>
+          <t>stirnwände komplettiert</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>stirnwand komplettiert</t>
+          <t>stirnwände komplettiert</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>stirnwand kompletiert</t>
+          <t>stirnwände nacharbeiten ( schleifen )</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>stirnwand komplettiert</t>
+          <t>stirnwände nacharbeiten ( schleifen )</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>stirnwand nacharbeiten.</t>
+          <t>strom und gasdüse reinigen</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>stirnwand nacharbeiten.</t>
+          <t>strom und gasdüse reinigen</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>stirnwand nachgearbeitet und komplettiert</t>
+          <t>stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>stirnwand nachgearbeitet und komplettiert</t>
+          <t>stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5218,102 +5218,102 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>stirnwand von draußen komplettiert</t>
+          <t>stw er 3 leute helfen aus</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>stirnwand von draußen komplettiert</t>
+          <t>stw er 3 leute helfen aus</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>stirnwände komplettiert</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>stirnwände komplettiert</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>stirnwände nacharbeiten ( schleifen )</t>
+          <t>nacharbeiten stw</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>stirnwände nacharbeiten ( schleifen )</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>strom und gasdüse gereinigt</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>strom und gasdüse gereinigt</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>strom und gasdüse reinigen</t>
+          <t>stw nacharbeiten (kratzer )</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>strom und gasdüse reinigen</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>stromausfall</t>
+          <t>stw nachgearbeitet</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>stromausfall</t>
+          <t>stw nachgearbeitet</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>stromdüse fest gebrannt</t>
+          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>stromdüse fest gebrannt</t>
+          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5323,12 +5323,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>stw er 3 leute helfen aus</t>
+          <t>stw nachgearbeitet (kratzer)</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>stw er 3 leute helfen aus</t>
+          <t>stw nachgearbeitet (kratzer)</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5338,27 +5338,27 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stw rungen eingebaut</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stw rungen eingebaut</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>nacharbeiten stw</t>
+          <t>stw von draußen komplettiert</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stw von draußen komplettiert</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5368,27 +5368,27 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw-test robotech an der anlage</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw-test robotech an der anlage</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer )</t>
+          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5398,72 +5398,72 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet</t>
+          <t>stw. mit 5 knoten</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet</t>
+          <t>stw. mit 5 knoten</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
+          <t>stw.-mit 5 knoten</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
+          <t>stw.-mit 5 knoten</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet (kratzer)</t>
+          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet (kratzer)</t>
+          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>stw rungen eingebaut</t>
+          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>stw rungen eingebaut</t>
+          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>stw von draußen komplettiert</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>stw von draußen komplettiert</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5473,12 +5473,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>stw-test robotech an der anlage</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>stw-test robotech an der anlage</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5488,27 +5488,27 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
+          <t>störung .robotech an der anlage.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
+          <t>störung .robotech an der anlage.</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>stw. mit 5 knoten</t>
+          <t>störung a-6 . robotech informiert.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>stw. mit 5 knoten</t>
+          <t>störung a-6 . robotech informiert.</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5518,27 +5518,27 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>stw.-mit 5 knoten</t>
+          <t>störung abholen knoten 3, robtech informiert</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>stw.-mit 5 knoten</t>
+          <t>störung abholen knoten 3, robtech informiert</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
+          <t>störung bei leoniefahrt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
+          <t>störung bei leoniefahrt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -5548,12 +5548,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
+          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
+          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5563,12 +5563,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true</t>
+          <t>störung beim abholen in op120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true</t>
+          <t>störung beim abholen in op120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5578,72 +5578,72 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>störung .robotech an der anlage.</t>
+          <t>störung beim abholen von knoten 3 in op 70</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>störung .robotech an der anlage.</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>störung a-6 . robotech informiert.</t>
+          <t>störung beim abholen von blech, robtech informiert</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>störung a-6 . robotech informiert.</t>
+          <t>störung beim abholen von blech, robtech informiert</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>störung abholen knoten 3, robtech informiert</t>
+          <t>störung beim abholen von knoten 1 und 3</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>störung abholen knoten 3, robtech informiert</t>
+          <t>störung beim abholen von knoten 1 und 3</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>störung bei leoniefahrt, robotertechniker informiert</t>
+          <t>störung beim abholen von knoten 3</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>störung bei leoniefahrt, robotertechniker informiert</t>
+          <t>störung beim abholen von knoten 3</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5653,27 +5653,27 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
+          <t>störung beim andrücken von stw-mt oben links</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
+          <t>störung beim andrücken von stw-mt oben links</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>störung beim abholen in op120.1 , robtech informiert</t>
+          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>störung beim abholen in op120.1 , robtech informiert</t>
+          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5683,27 +5683,27 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3 in op 70</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5713,12 +5713,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>störung beim abholen von blech, robtech informiert</t>
+          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>störung beim abholen von blech, robtech informiert</t>
+          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5728,57 +5728,57 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 1 und 3</t>
+          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 1 und 3</t>
+          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3</t>
+          <t>störung beim knoten abholen in op 70, robtech informiert</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3</t>
+          <t>störung beim knoten abholen in op 70, robtech informiert</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>störung beim andrücken von stw-mt oben links</t>
+          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>störung beim andrücken von stw-mt oben links</t>
+          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
+          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
+          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5788,12 +5788,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
+          <t>störung beim versuchen zu schweißen</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
+          <t>störung beim versuchen zu schweißen</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5803,27 +5803,27 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
+          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
+          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
+          <t>störung drehachse. robotech informiert.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
+          <t>störung drehachse. robotech informiert.</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -5833,12 +5833,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
+          <t>störung durch drahtsehne im brenner, tauschen</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
+          <t>störung durch drahtsehne im brenner, tauschen</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -5848,12 +5848,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>störung beim knoten abholen in op 70, robtech informiert</t>
+          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>störung beim knoten abholen in op 70, robtech informiert</t>
+          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -5863,27 +5863,27 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
+          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
+          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
+          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
+          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -5893,42 +5893,42 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>störung beim versuchen zu schweißen</t>
+          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>störung beim versuchen zu schweißen</t>
+          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
+          <t>störung schweißdraht</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
+          <t>störung schweißdraht</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>störung drehachse. robotech informiert.</t>
+          <t>störung stiftzieher</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>störung drehachse. robotech informiert.</t>
+          <t>störung stiftzieher</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -5938,42 +5938,42 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>störung durch drahtsehne im brenner, tauschen</t>
+          <t>störung wegen stromausfall</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>störung durch drahtsehne im brenner, tauschen</t>
+          <t>störung wegen stromausfall</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
+          <t>störung wegen stromausfall robo tech. an der anlage.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
+          <t>störung wegen stromausfall robo tech. an der anlage.</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
+          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
+          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -5983,42 +5983,42 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
+          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
+          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
+          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
+          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>störung schweißdraht</t>
+          <t>störungen beim abholen in op 25, robtech informiert</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>störung schweißdraht</t>
+          <t>störungen beim abholen in op 25, robtech informiert</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6028,42 +6028,42 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>störung stiftzieher</t>
+          <t>stütze andrücken störung</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>störung stiftzieher</t>
+          <t>stütze andrücken störung</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall</t>
+          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall</t>
+          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall robo tech. an der anlage.</t>
+          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall robo tech. an der anlage.</t>
+          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6073,12 +6073,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
+          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
+          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6088,42 +6088,42 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
+          <t>tauschbox</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
+          <t>tauschbox</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
+          <t>tb. verschmutzt (schleifen)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
+          <t>tb. verschmutzt (schleifen)</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>störungen beim abholen in op 25, robtech informiert</t>
+          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>störungen beim abholen in op 25, robtech informiert</t>
+          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6133,27 +6133,27 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>stütze andrücken störung</t>
+          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>stütze andrücken störung</t>
+          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
+          <t>tor sensor nicht geschaltet</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
+          <t>tor sensor nicht geschaltet</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6163,72 +6163,72 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
+          <t>torsensor schaltet nicht</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
+          <t>torsensor schaltet nicht</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
+          <t>torsensor schaltet nicht robotech in der anlage</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
+          <t>torsensor schaltet nicht robotech in der anlage</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>tauschbox</t>
+          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>tauschbox</t>
+          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>tb. verschmutzt (schleifen)</t>
+          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>tb. verschmutzt (schleifen)</t>
+          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>teil vom arm krumm. ursache unbekannnt. beim abholen der 1. stw von op 50</t>
+          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>teil vom arm krumm. ursache unbekannnt. beim abholen der 1. stw von op 50</t>
+          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6238,12 +6238,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
+          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
+          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6253,27 +6253,27 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
+          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
+          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>tor sensor nicht geschaltet</t>
+          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>tor sensor nicht geschaltet</t>
+          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -6283,57 +6283,57 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht</t>
+          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht</t>
+          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht robotech in der anlage</t>
+          <t>vakuum nicht vorhanden</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht robotech in der anlage</t>
+          <t>vakuum nicht vorhanden</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
+          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
+          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
+          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
+          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6343,57 +6343,57 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
+          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
+          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
+          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
+          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
+          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
+          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
+          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
+          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6403,102 +6403,102 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
+          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
+          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden</t>
+          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden</t>
+          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
+          <t>vakuum nicht vorhanden bei blechen 953</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
+          <t>vakuum nicht vorhanden bei blechen 953</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
+          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
+          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
+          <t>vakuum nicht vorhanden in op-50</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
+          <t>vakuum nicht vorhanden in op-50</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
+          <t>vakuum nicht vorhanden in op.50</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
+          <t>vakuum nicht vorhanden in op.50</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
+          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
+          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6508,12 +6508,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
+          <t>vakuum probleme. robtech informiert</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
+          <t>vakuum probleme. robtech informiert</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6523,87 +6523,87 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
+          <t>vakuumkreis 1 schaltet nicht</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
+          <t>vakuumkreis 1 schaltet nicht</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei blechen 953</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei blechen 953</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op-50</t>
+          <t>vakuumkreis 1 schaltet nicht in op 50</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op-50</t>
+          <t>vakuumkreis 1 schaltet nicht in op 50</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op.50</t>
+          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op.50</t>
+          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6613,27 +6613,27 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
+          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
+          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>vakuum probleme. robtech informiert</t>
+          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>vakuum probleme. robtech informiert</t>
+          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6643,72 +6643,72 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht</t>
+          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht</t>
+          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
+          <t>vakuumkreis 2 schaltet nicht</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
+          <t>vakuumkreis 2 schaltet nicht</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
+          <t>vakuumkreis 2 schaltet nicht in op.50</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
+          <t>vakuumkreis 2 schaltet nicht in op.50</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
+          <t>vakuumkreis 3 schaltet nicht</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
+          <t>vakuumkreis 3 schaltet nicht</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op 50</t>
+          <t>vakuumstörung in op 50, robtech in der anlage</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op 50</t>
+          <t>vakuumstörung in op 50, robtech in der anlage</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6718,12 +6718,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
+          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
+          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6733,12 +6733,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
+          <t>warnstreik</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
+          <t>warnstreik</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6748,12 +6748,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
+          <t>warten auf 230 bleche</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
+          <t>warten auf 230 bleche</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6763,12 +6763,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
+          <t>warten auf bleche 953</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
+          <t>warten auf bleche 953</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6778,72 +6778,72 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht</t>
+          <t>warten auf coll detected op 130.1</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht</t>
+          <t>warten auf coll detected op 130.1</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht in op.50</t>
+          <t>warten auf eckrungen</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht in op.50</t>
+          <t>warten auf eckrungen</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>vakuumkreis 3 schaltet nicht</t>
+          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>vakuumkreis 3 schaltet nicht</t>
+          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>vakuumstörung in op 50, robtech in der anlage</t>
+          <t>warten auf robtech</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>vakuumstörung in op 50, robtech in der anlage</t>
+          <t>warten auf robtech</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
+          <t>warten auf rungen (nur ein staplerfahrer)</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
+          <t>warten auf rungen (nur ein staplerfahrer)</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -6853,12 +6853,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>warnstreik</t>
+          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>warnstreik</t>
+          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6868,27 +6868,27 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>warten auf 230 bleche</t>
+          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>warten auf 230 bleche</t>
+          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>warten auf bleche 953</t>
+          <t>warten auf stüzten l5 endnummer 740</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>warten auf bleche 953</t>
+          <t>warten auf stüzten l5 endnummer 740</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6898,12 +6898,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>warten auf coll detected op 130.1</t>
+          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>warten auf coll detected op 130.1</t>
+          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6913,57 +6913,57 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>warten auf eckrungen</t>
+          <t>wartung</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>warten auf eckrungen</t>
+          <t>wartung</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
+          <t>wartungsplan</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
+          <t>wartungsplan</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>794</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>warten auf robtech</t>
+          <t>wartungsplan + tauschbox</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>warten auf robtech</t>
+          <t>wartungsplan + tauschbox</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>warten auf rungen (nur ein staplerfahrer)</t>
+          <t>wartungsplan und tauschbox</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>warten auf rungen (nur ein staplerfahrer)</t>
+          <t>wartungsplan und tauschbox</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6973,117 +6973,117 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
+          <t>wartungsplan.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
+          <t>wartungsplan.</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>warten auf stüzten l5 endnummer 740</t>
+          <t>reinigen und werkzeug einschließen</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>warten auf stüzten l5 endnummer 740</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
+          <t>werkzeug einschließen und reinigung</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
+          <t>werkzeug einschließen und reinigung</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>wartung</t>
+          <t>werkzeug wegpacken, reinigen</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>wartung</t>
+          <t>werkzeug wegpacken, reinigen</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>wartungsplan</t>
+          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>wartungsplan</t>
+          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>802</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>wartungsplan + tauschbox</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>wartungsplan + tauschbox</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>wartungsplan und tauschbox</t>
+          <t>zwei neue mitarbeiter anlernen</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>wartungsplan und tauschbox</t>
+          <t>zwei neue mitarbeiter anlernen</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7093,195 +7093,75 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>wartungsplan.</t>
+          <t>zylinder defekt (robotech in der anlage,)</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>wartungsplan.</t>
+          <t>zylinder defekt (robotech in der anlage,)</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>reinigen und werkzeug einschließen</t>
+          <t>zündfehler &gt;ohne meldung</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>zündfehler &gt;ohne meldung</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigung</t>
+          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigung</t>
+          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>werkzeug wegpacken, reinigen</t>
+          <t>zündfehler. stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>werkzeug wegpacken, reinigen</t>
+          <t>zündfehler. stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
-        </is>
-      </c>
-      <c r="C450" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>wöchentliche reinigung</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>wöchentliche reinigung</t>
-        </is>
-      </c>
-      <c r="C451" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>zwei neue mitarbeiter anlernen</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>zwei neue mitarbeiter anlernen</t>
-        </is>
-      </c>
-      <c r="C452" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>zylinder defekt (robotech in der anlage,)</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>zylinder defekt (robotech in der anlage,)</t>
-        </is>
-      </c>
-      <c r="C453" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>zündfehler</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>zündfehler</t>
-        </is>
-      </c>
-      <c r="C454" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>zündfehler &gt;ohne meldung</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>zündfehler &gt;ohne meldung</t>
-        </is>
-      </c>
-      <c r="C455" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
-        </is>
-      </c>
-      <c r="C456" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>zündfehler. stromdüse fest gebrannt</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>zündfehler. stromdüse fest gebrannt</t>
-        </is>
-      </c>
-      <c r="C457" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/lstm ready data/mta_mapping_bemerkung.xlsx
+++ b/data/lstm ready data/mta_mapping_bemerkung.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C449"/>
+  <dimension ref="A1:C451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,27 +988,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst + folgefehler beheben</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
+          <t>bedienerschutz ausgelöst + folgefehler beheben</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>bedienerschutz ausgelöst + folgefehler beheben</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>bedienerschutz ausgelöst . folgefehler beheben</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2023,12 +2023,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
+          <t>in op.120-1 schweißnahtqualität schlecht qt. unten nachschweißen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
+          <t>in op.120-1 schweißnahtqualität schlecht qt. unten nachschweißen</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2038,112 +2038,112 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kein bediener, reinigung</t>
+          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kein bediener, reinigung</t>
+          <t>kabelbruch in der elektrik ( robo tech und elektriker in der anlage.)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kein gas</t>
+          <t>kein bediener, reinigung</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kein gas</t>
+          <t>kein bediener, reinigung</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kein gas mehr, durch robtech informiert</t>
+          <t>kein gas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kein gas mehr, durch robtech informiert</t>
+          <t>kein gas</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kein monteur</t>
+          <t>kein gas mehr, durch robtech informiert</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kein monteur</t>
+          <t>kein gas mehr, durch robtech informiert</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kein montuer</t>
+          <t>kein monteur</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kein montuer</t>
+          <t>kein monteur</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kein vakuum</t>
+          <t>kein montuer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kein vakuum</t>
+          <t>kein montuer</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kein vakuum bleche kleben aneinander</t>
+          <t>kein vakuum</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kein vakuum bleche kleben aneinander</t>
+          <t>kein vakuum</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kein vakuum, bleche kleben aneinander</t>
+          <t>kein vakuum bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,18 +2152,18 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>keine daten robotech an der anlage</t>
+          <t>kein vakuum, bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>keine daten robotech an der anlage</t>
+          <t>kein vakuum bleche kleben aneinander</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2173,57 +2173,57 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>keine l-5 füsse für stüzen.</t>
+          <t>keine daten robotech an der anlage</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>keine l-5 füsse für stüzen.</t>
+          <t>keine daten robotech an der anlage</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>keine mes- daten</t>
+          <t>keine l-5 füsse für stüzen.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>keine mes- daten</t>
+          <t>keine l-5 füsse für stüzen.</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt (robotech informiert)</t>
+          <t>keine mes- daten</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt (robotech informiert)</t>
+          <t>keine mes- daten</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt in op 50</t>
+          <t>knoten 3 klemmt (robotech informiert)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>knoten 3 klemmt in op 50</t>
+          <t>knoten 3 klemmt (robotech informiert)</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2233,72 +2233,72 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>knotengreifer 3 störung beim abholen in op 70</t>
+          <t>knoten 3 klemmt in op 50</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>knotengreifer 3 störung beim abholen in op 70</t>
+          <t>knoten 3 klemmt in op 50</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>knotenschweißgerät defekt elektriker informiert</t>
+          <t>knotengreifer 3 störung beim abholen in op 70</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>knotenschweißgerät defekt elektriker informiert</t>
+          <t>knotengreifer 3 störung beim abholen in op 70</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kollision</t>
+          <t>knotenschweißgerät defekt elektriker informiert</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>kollision</t>
+          <t>knotenschweißgerät defekt elektriker informiert</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kollision ( robotech informiert)</t>
+          <t>kollision</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kollision ( robotech informiert)</t>
+          <t>kollision</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kollision (brenner prüfen durch robotech.)</t>
+          <t>kollision ( robotech informiert)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kollision (brenner prüfen durch robotech.)</t>
+          <t>kollision ( robotech informiert)</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2308,12 +2308,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
+          <t>kollision (brenner prüfen durch robotech.)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
+          <t>kollision (brenner prüfen durch robotech.)</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2323,42 +2323,42 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
+          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
+          <t>kollision in op 50 beim knoten auflegen ( achse auseinander gefahren, kabelbinder zum fixieren gerissen ), robtech informiert</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kollision mit stw l4</t>
+          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kollision mit stw l4</t>
+          <t>kollision knoten 1 schweißpunkt 2 l.4 robotech informiert</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kollisionsabfrage</t>
+          <t>kollision mit stw l4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kollisionsabfrage</t>
+          <t>kollision mit stw l4</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2368,42 +2368,42 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
+          <t>kollisionsabfrage</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
+          <t>kollisionsabfrage</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kran defekt (elektriker an de anlage.)</t>
+          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kran defekt (elektriker an de anlage.)</t>
+          <t>kontaktrohr und gasdüse gereinigt bei r 06 und r 07</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kran fernbedienung defekt, elektriker informiert</t>
+          <t>kran defekt (elektriker an de anlage.)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kran fernbedienung defekt, elektriker informiert</t>
+          <t>kran defekt (elektriker an de anlage.)</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2413,12 +2413,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
+          <t>kran fernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
+          <t>kran fernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2428,12 +2428,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kran störung, elektriker informiert</t>
+          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>kran störung, elektriker informiert</t>
+          <t>kran motorhalterung einseitig gebrochen, schlosser informiert</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2443,12 +2443,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
+          <t>kran störung, elektriker informiert</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
+          <t>kran störung, elektriker informiert</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2458,12 +2458,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kranfernbedienung defekt, elektriker informiert</t>
+          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kranfernbedienung defekt, elektriker informiert</t>
+          <t>kran störung, schlosser informiert ( kran nichtmehr parallel und lässt sich nicht mehr bewegen</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2473,57 +2473,57 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kratzer in der stirnwand ausbessern.</t>
+          <t>kranfernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kratzer in der stirnwand ausbessern.</t>
+          <t>kranfernbedienung defekt, elektriker informiert</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kratzer in stw nacharbeiten</t>
+          <t>kratzer in der stirnwand ausbessern.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kratzer in stw nacharbeiten</t>
+          <t>kratzer in der stirnwand ausbessern.</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>l5 muttern organisieren</t>
+          <t>kratzer in stw nacharbeiten</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>l5 muttern organisieren</t>
+          <t>kratzer in stw nacharbeiten</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>laser störung</t>
+          <t>l5 muttern organisieren</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>laser störung</t>
+          <t>l5 muttern organisieren</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2533,102 +2533,102 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>laserscanner messwerte störung, robtech informiert</t>
+          <t>laser störung</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>laserscanner messwerte störung, robtech informiert</t>
+          <t>laser störung</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>leoni störung</t>
+          <t>laserscanner messwerte störung, robtech informiert</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>leoni störung</t>
+          <t>laserscanner messwerte störung, robtech informiert</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
+          <t>leoni störung</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
+          <t>leoni störung</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>leonie fahrt störung</t>
+          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>leonie fahrt störung</t>
+          <t>leonie defekt ( roboter vermutlich mit schlauchpaket hängengeblieben ) robtech informiert</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>leonie störung</t>
+          <t>leonie fahrt störung</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>leonie störung</t>
+          <t>leonie fahrt störung</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>leonie störung robotech in der anlage</t>
+          <t>leonie störung</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>leonie störung robotech in der anlage</t>
+          <t>leonie störung</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
+          <t>leonie störung robotech in der anlage</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
+          <t>leonie störung robotech in der anlage</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2638,102 +2638,102 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>leonie störungen</t>
+          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>leonie störungen</t>
+          <t>leonie störung, leoniefahtr im handbetrieb durchgeführt</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>leonifehler ohne fehlermeldung.</t>
+          <t>leonie störungen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>leonifehler ohne fehlermeldung.</t>
+          <t>leonie störungen</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>leonifehler, robtech informiert,warten auf robtech</t>
+          <t>leonifehler ohne fehlermeldung.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>leonifehler, robtech informiert,warten auf robtech</t>
+          <t>leonifehler ohne fehlermeldung.</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>leonifehler, robtech informiert,warten auf robtech</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>leonifehler.</t>
+          <t>leonifehler, robtech informiert,warten auf robtech</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
+          <t>leonifehler.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
+          <t>leonifehler.</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
+          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
+          <t>linearachsstörung ( achse verfährt nicht in automatic betrieb ), robtech informiert</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>liner 4 einseitig.</t>
+          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>liner 4 einseitig.</t>
+          <t>linearantriebsstörung op130.2 und op130.1 ( robotech an der anlage.)</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2743,42 +2743,42 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>maschine leer gefahren</t>
+          <t>liner 4 einseitig.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>maschine leer gefahren</t>
+          <t>liner 4 einseitig.</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>mehraufwand nacharbeiten</t>
+          <t>maschine leer gefahren</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>mehraufwand nacharbeiten</t>
+          <t>maschine leer gefahren</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
+          <t>mehraufwand nacharbeiten</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
+          <t>mehraufwand nacharbeiten</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2788,12 +2788,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( qt oben )</t>
+          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( qt oben )</t>
+          <t>mehraufwand nachschweißen ( mittelnahrt . n.i.o.)</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2803,72 +2803,72 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
+          <t>mehraufwand nachschweißen . ( qt oben )</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
+          <t>mehraufwand nachschweißen . ( qt oben )</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze .)</t>
+          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>mehraufwand nachschweißen . ( stuetze .)</t>
+          <t>mehraufwand nachschweißen . ( stuetze - re.)</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
+          <t>mehraufwand nachschweißen . ( stuetze .)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
+          <t>mehraufwand nachschweißen . ( stuetze .)</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>mes daten störung</t>
+          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>mes daten störung</t>
+          <t>mehraufwand stirnwand nachschweißen ( qt )</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
+          <t>mes daten störung</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
+          <t>mes daten störung</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2878,42 +2878,42 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
+          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
+          <t>messeinheit eingefahren signal nicht erhalten, ( gepuscht ) bei einer 5 knoten stirnwand</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>messwerte laser n.i.o (robotech informiert)</t>
+          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>messwerte laser n.i.o (robotech informiert)</t>
+          <t>messwert unplausibel. messeinrichtung sauber gemacht.</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>mitarbeiterpause aufgrund der temperaturen</t>
+          <t>messwerte laser n.i.o (robotech informiert)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>mitarbeiterpause aufgrund der temperaturen</t>
+          <t>messwerte laser n.i.o (robotech informiert)</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2923,12 +2923,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
+          <t>mitarbeiterpause aufgrund der temperaturen</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
+          <t>mitarbeiterpause aufgrund der temperaturen</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2938,12 +2938,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 - 230 trapez - bleche ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2953,12 +2953,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>monatliche wartungsplan</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>monatliche wartungsplan</t>
+          <t>mittelnaht nicht richtig verschweißt ( 229 trapez - bleche zu schmall. ), bleche aus anlage geräumt</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2968,12 +2968,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nacharbeitszellen kein strom, elektriker informiert</t>
+          <t>monatliche wartungsplan</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nacharbeitszellen kein strom, elektriker informiert</t>
+          <t>monatliche wartungsplan</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2983,12 +2983,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
+          <t>nacharbeitszellen kein strom, elektriker informiert</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
+          <t>nacharbeitszellen kein strom, elektriker informiert</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2998,12 +2998,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
+          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
+          <t>nachteachen ( in op 120.1 ) qt oben . robtech in der anlage</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3013,42 +3013,42 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>niecht activ nur op.130-2. so übernomen</t>
+          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>niecht activ nur op.130-2. so übernomen</t>
+          <t>nachteachen,( knotten-1 in op.50 ) robtech in der anlage</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>not halt störung und folge fehler beheben</t>
+          <t>niecht activ nur op.130-2. so übernomen</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>not halt störung und folge fehler beheben</t>
+          <t>niecht activ nur op.130-2. so übernomen</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
+          <t>not halt störung und folge fehler beheben</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
+          <t>not halt störung und folge fehler beheben</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3058,87 +3058,87 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>nur 1 schweißer an der anlage</t>
+          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>nur 1 schweißer an der anlage</t>
+          <t>not-aus anschlussbox 1 ausgelöst (robotech informiert.)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>nur ein schweißer an der anlage</t>
+          <t>nur 1 schweißer an der anlage</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>nur ein schweißer an der anlage</t>
+          <t>nur 1 schweißer an der anlage</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>nur op-130-1. ist aktiv</t>
+          <t>nur ein schweißer an der anlage</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>nur op-130-1. ist aktiv</t>
+          <t>nur ein schweißer an der anlage</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>op passiv geschaltet</t>
+          <t>nur op-130-1. ist aktiv</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>op passiv geschaltet</t>
+          <t>nur op-130-1. ist aktiv</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-4</t>
+          <t>op passiv geschaltet</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-4</t>
+          <t>op passiv geschaltet</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-5</t>
+          <t>op passiv geschaltet l-4</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>op passiv geschaltet l-5</t>
+          <t>op passiv geschaltet l-4</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3148,57 +3148,57 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen .</t>
+          <t>op passiv geschaltet l-5</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen .</t>
+          <t>op passiv geschaltet l-5</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
+          <t>op.100-op110.- mehraufwand nachschweißen .</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
+          <t>op.100-op110.- mehraufwand nachschweißen .</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>op.50 problem mit schrittkette robotech informiert.</t>
+          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>op.50 problem mit schrittkette robotech informiert.</t>
+          <t>op.100-op110.- mehraufwand nachschweißen . ( stuetzen )</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
+          <t>op.50 problem mit schrittkette robotech informiert.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
+          <t>op.50 problem mit schrittkette robotech informiert.</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3208,12 +3208,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
+          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
+          <t>op10 rechts beim abholen eines bleches aus r 2.3 blech beim rausfahren verloren und dann mit vorrichtung auf dem blech was halb in den bereich hing draufgefahren. robtech informiert</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3223,12 +3223,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
+          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
+          <t>op25 schrittkette übersprungen (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3238,12 +3238,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>op50 vakuum störung</t>
+          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>op50 vakuum störung</t>
+          <t>op30 stiftzicher klemmt bei jedern re tb.</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3253,12 +3253,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
+          <t>op50 vakuum störung</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
+          <t>op50 vakuum störung</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3268,12 +3268,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
+          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
+          <t>parameter eingestellt wie weit die fahrachse verfährt, durch robtech</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3283,42 +3283,42 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
+          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
+          <t>poren r 06 und r 07 kontaktrohre wechseln, gasdüsen reinigen</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
+          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
+          <t>probleme beim abholen von knoten und beim ablegen von knoten 2 &amp; 3 in op 50</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
+          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
+          <t>probleme beim stützen andrücken. (robotech in der anlage. )</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3328,12 +3328,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>probleme mit dem laser .(robotech informiert</t>
+          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>probleme mit dem laser .(robotech informiert</t>
+          <t>probleme mit brenner. unererreichbarer punkt. robtech hat brenner gerichtet und leonie werte zurueck gesetzt</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3343,42 +3343,42 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
+          <t>probleme mit dem laser .(robotech informiert</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
+          <t>probleme mit dem laser .(robotech informiert</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
+          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
+          <t>probleme mit drucker. alle aufträge per hand auf etikett schreiben. stw stehen vorm tor</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>probleme mit gravierer</t>
+          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>probleme mit gravierer</t>
+          <t>probleme mit fernbedienung vom kran elektriker informiert</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3388,42 +3388,42 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr</t>
+          <t>probleme mit gravierer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr</t>
+          <t>probleme mit gravierer</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
+          <t>probleme mit kontaktrohr</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
+          <t>probleme mit kontaktrohr</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>probleme mit kran- funkstörung</t>
+          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>probleme mit kran- funkstörung</t>
+          <t>probleme mit kontaktrohr ( draht festgeschweißt )</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3433,12 +3433,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
+          <t>probleme mit kran- funkstörung</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
+          <t>probleme mit kran- funkstörung</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3448,87 +3448,87 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>probleme mit r 03 &amp; r 07 leoni</t>
+          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>probleme mit r 03 &amp; r 07 leoni</t>
+          <t>probleme mit op.120-1 op.130-1 warten auf robotech.</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht</t>
+          <t>probleme mit r 03 &amp; r 07 leoni</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht</t>
+          <t>probleme mit r 03 &amp; r 07 leoni</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
+          <t>probleme mit schweißdraht</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
+          <t>probleme mit schweißdraht</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht (robotech informiert)</t>
+          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht (robotech informiert)</t>
+          <t>probleme mit schweißdraht ( förderkabel für draht defekt.)</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht .robotech .an der anlage</t>
+          <t>probleme mit schweißdraht (robotech informiert)</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht .robotech .an der anlage</t>
+          <t>probleme mit schweißdraht (robotech informiert)</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
+          <t>probleme mit schweißdraht .robotech .an der anlage</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
+          <t>probleme mit schweißdraht .robotech .an der anlage</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3538,12 +3538,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>probleme mit sensor am tor (robotech infor)</t>
+          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>probleme mit sensor am tor (robotech infor)</t>
+          <t>probleme mit schweißdraht, brenner gewechselt ( 2 mal ) da er mit dem 1. neuen brenner auch in die collisionsabfrage gefahren ist</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3553,87 +3553,87 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse</t>
+          <t>probleme mit sensor am tor (robotech infor)</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse</t>
+          <t>probleme mit sensor am tor (robotech infor)</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
+          <t>probleme mit stromdüse</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
+          <t>probleme mit stromdüse</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( tauschen.)</t>
+          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>probleme mit stromdüse ( tauschen.)</t>
+          <t>probleme mit stromdüse ( dichtgeschweißt )</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>programm fehler (robtech an der anlage)</t>
+          <t>probleme mit stromdüse ( tauschen.)</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>programm fehler (robtech an der anlage)</t>
+          <t>probleme mit stromdüse ( tauschen.)</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>programm störung, robtech informiert</t>
+          <t>programm fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>programm störung, robtech informiert</t>
+          <t>programm fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>programm verlust (robtech an der anlage)</t>
+          <t>programm störung, robtech informiert</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>programm verlust (robtech an der anlage)</t>
+          <t>programm störung, robtech informiert</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3643,12 +3643,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>programmtörung von r 05, robtech informiert</t>
+          <t>programm verlust (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>programmtörung von r 05, robtech informiert</t>
+          <t>programm verlust (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3658,12 +3658,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
+          <t>programmtörung von r 05, robtech informiert</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
+          <t>programmtörung von r 05, robtech informiert</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3673,12 +3673,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
+          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
+          <t>qs prüft bleche auf maßhaltigkeit 230 n.i.o. neue i.o. bleche in die anlage gelegt</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3688,12 +3688,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>querträger für l5 fählt</t>
+          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>querträger für l5 fählt</t>
+          <t>querprofil nicht nah genug an trapezblech gefahren. robtech informiert</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3703,12 +3703,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>querträger oben einstellen durch robtech</t>
+          <t>querträger für l5 fählt</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>querträger oben einstellen durch robtech</t>
+          <t>querträger für l5 fählt</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3718,12 +3718,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
+          <t>querträger oben einstellen durch robtech</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
+          <t>querträger oben einstellen durch robtech</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3733,12 +3733,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
+          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
+          <t>querträger oben nach dem drehen abgesackt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3748,12 +3748,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
+          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
+          <t>querträger oben nach drehen abgesagt, robtech informiert</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3763,12 +3763,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
+          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
+          <t>querträgerabstand zu groß, trapezblech oben links hatte sich verhackt, robtech informiert</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3778,12 +3778,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>r 6 und r 7 kontaktrohr gewechselt</t>
+          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>r 6 und r 7 kontaktrohr gewechselt</t>
+          <t>r 05 fährt mit blech nicht raus obwohl spanner alle offen sind und linearachse weggefahren ist.</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3793,12 +3793,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>r.06 - probleme mit stromdüse</t>
+          <t>r 6 und r 7 kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>r.06 - probleme mit stromdüse</t>
+          <t>r 6 und r 7 kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3808,12 +3808,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
+          <t>r.06 - probleme mit stromdüse</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
+          <t>r.06 - probleme mit stromdüse</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3823,12 +3823,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
+          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
+          <t>r.06 - störung in op.130-1. (robotech an der anlage.)</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3838,12 +3838,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>reingung</t>
+          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>reingung</t>
+          <t>r.07 gasdüse und kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3853,252 +3853,252 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>reinigen</t>
+          <t>reingung</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>reinigen</t>
+          <t>reingung</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>203</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>reinigen + werkzeug einschließen</t>
+          <t>reinigen</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>reinigen + werkzeug einschließen</t>
+          <t>reinigen</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14</v>
+        <v>202</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>reinigen,werkzeug wegpacken</t>
+          <t>reinigen + werkzeug einschließen</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>reinigen,werkzeug wegpacken</t>
+          <t>reinigen + werkzeug einschließen</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>reinigung</t>
+          <t>reinigen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>reinigung</t>
+          <t>reinigen,werkzeug wegpacken</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>527</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>reinigung + werkzeug einschließen</t>
+          <t>reinigung</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>reinigung + werkzeug einschließen</t>
+          <t>reinigung</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>88</v>
+        <v>534</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>reinigung von außen</t>
+          <t>reinigung + werkzeug einschließen</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>reinigung von außen</t>
+          <t>reinigung + werkzeug einschließen</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>reinigung.</t>
+          <t>reinigung von außen</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>reinigung.</t>
+          <t>reinigung von außen</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>robotech an der anlage neue bleche testen (186-190.)</t>
+          <t>reinigung.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>robotech an der anlage neue bleche testen (186-190.)</t>
+          <t>reinigung.</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
+          <t>robotech an der anlage neue bleche testen (186-190.)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
+          <t>robotech an der anlage neue bleche testen (186-190.)</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>robotechniker in der anlage</t>
+          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>robotechniker in der anlage</t>
+          <t>robotech in der anlage . qt . teachen, schweißnahtposition</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
+          <t>robotechniker in der anlage</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
+          <t>robotechniker in der anlage</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
+          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
+          <t>roboter 6 und 7 strom - gasdüse gereinigt ( poren )</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>robtech an der anlage</t>
+          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>robtech an der anlage</t>
+          <t>roboter- 6 und-7 störung ( a3 ) bei blech 964-965.</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>robtech bei der anlage</t>
+          <t>robtech an der anlage</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>robtech bei der anlage</t>
+          <t>robtech an der anlage</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>robtech informiert</t>
+          <t>robtech bei der anlage</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>robtech informiert</t>
+          <t>robtech bei der anlage</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
+          <t>robtech informiert</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
+          <t>robtech informiert</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sauger beim abholen aus op 25 vakuum verloren</t>
+          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>sauger beim abholen aus op 25 vakuum verloren</t>
+          <t>robtechnik vor ort, alle op mussen neu referenziert werden, reinigung</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4108,12 +4108,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sauger defekt</t>
+          <t>sauger beim abholen aus op 25 vakuum verloren</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>sauger defekt</t>
+          <t>sauger beim abholen aus op 25 vakuum verloren</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4123,12 +4123,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sauger defekt oder verdreht</t>
+          <t>sauger defekt</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>sauger defekt oder verdreht</t>
+          <t>sauger defekt</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4138,72 +4138,72 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
+          <t>sauger defekt oder verdreht</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
+          <t>sauger defekt oder verdreht</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>schrittketten fehler (anlage so übernommen)</t>
+          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>schrittketten fehler (anlage so übernommen)</t>
+          <t>scheißstörung beim schweißen des ersten knotens, robtech informiert</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>schrittketten fehler (robtech an der anlage)</t>
+          <t>schrittketten fehler (anlage so übernommen)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>schrittketten fehler (robtech an der anlage)</t>
+          <t>schrittketten fehler (anlage so übernommen)</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>schrittketten fehler und m1 antrieb fehler</t>
+          <t>schrittketten fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>schrittketten fehler und m1 antrieb fehler</t>
+          <t>schrittketten fehler (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>schrittketten störung (robtech an der anlage)</t>
+          <t>schrittketten fehler und m1 antrieb fehler</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>schrittketten störung (robtech an der anlage)</t>
+          <t>schrittketten fehler und m1 antrieb fehler</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4213,12 +4213,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
+          <t>schrittketten störung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
+          <t>schrittketten störung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4228,12 +4228,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>schweißdraht festgebrannt</t>
+          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>schweißdraht festgebrannt</t>
+          <t>schrittketten störung und zylinder wechseln (robtech vor ort)</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4243,12 +4243,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>schweißdraht wechseln</t>
+          <t>schweißdraht festgebrannt</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>schweißdraht wechseln</t>
+          <t>schweißdraht festgebrannt</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4258,12 +4258,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
+          <t>schweißdraht wechseln</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
+          <t>schweißdraht wechseln</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4273,12 +4273,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
+          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
+          <t>schweißgerät bei denn knoten läuft nicht (warten auf elektrika)</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4288,12 +4288,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
+          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
+          <t>schweißnahtqualität schlecht ( viel nacharbeit ) / kontaktrohr gewechselt</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4303,12 +4303,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht, robtech informiert</t>
+          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>schweißnahtqualität schlecht, robtech informiert</t>
+          <t>schweißnahtqualität schlecht nacharbeiten ( zuschnittmaße . von 953 blech n.i.o )</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4318,12 +4318,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>schweißnähte nachtecachen</t>
+          <t>schweißnahtqualität schlecht, robtech informiert</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>schweißnähte nachtecachen</t>
+          <t>schweißnahtqualität schlecht, robtech informiert</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4333,12 +4333,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>schweißnähte schlecht, brenner tauschen</t>
+          <t>schweißnähte nachtecachen</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>schweißnähte schlecht, brenner tauschen</t>
+          <t>schweißnähte nachtecachen</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4348,12 +4348,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>schweißnähte teachen durch robtech</t>
+          <t>schweißnähte schlecht, brenner tauschen</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>schweißnähte teachen durch robtech</t>
+          <t>schweißnähte schlecht, brenner tauschen</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4363,12 +4363,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
+          <t>schweißnähte teachen durch robtech</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
+          <t>schweißnähte teachen durch robtech</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4378,147 +4378,147 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>schweißstörung</t>
+          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>schweißstörung</t>
+          <t>schweißnähte. qt. ( r 06 ) nachteachen durch robtech</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>schweißstörung (robtech an der anlage)</t>
+          <t>schweißstörung</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>schweißstörung (robtech an der anlage)</t>
+          <t>schweißstörung</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>schweißstörung .</t>
+          <t>schweißstörung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>schweißstörung .</t>
+          <t>schweißstörung (robtech an der anlage)</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius</t>
+          <t>schweißstörung .</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius</t>
+          <t>schweißstörung .</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius in op.120-1</t>
+          <t>schweißstörung am fronius</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius in op.120-1</t>
+          <t>schweißstörung am fronius</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius robotech in der anlage</t>
+          <t>schweißstörung am fronius in op.120-1</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>schweißstörung am fronius robotech in der anlage</t>
+          <t>schweißstörung am fronius in op.120-1</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>schweißstörung bei op120.2</t>
+          <t>schweißstörung am fronius robotech in der anlage</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>schweißstörung bei op120.2</t>
+          <t>schweißstörung am fronius robotech in der anlage</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>schweißstörung durch bauteil</t>
+          <t>schweißstörung bei op120.2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>schweißstörung durch bauteil</t>
+          <t>schweißstörung bei op120.2</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>schweißstörung in op-120.1 , robtech informiert</t>
+          <t>schweißstörung durch bauteil</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>schweißstörung in op-120.1 , robtech informiert</t>
+          <t>schweißstörung durch bauteil</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>schweißstörung in op.120-2</t>
+          <t>schweißstörung in op-120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>schweißstörung in op.120-2</t>
+          <t>schweißstörung in op-120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4528,12 +4528,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>schweißstörung robotech informiert.</t>
+          <t>schweißstörung in op.120-2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>schweißstörung robotech informiert.</t>
+          <t>schweißstörung in op.120-2</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4543,12 +4543,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>schweißstörung.</t>
+          <t>schweißstörung robotech informiert.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>schweißstörung.</t>
+          <t>schweißstörung robotech informiert.</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4558,12 +4558,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
+          <t>schweißstörung.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
+          <t>schweißstörung.</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4573,12 +4573,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
+          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
+          <t>schweißt eine stelle nicht da wo es soll (robtech wurde info)</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4588,12 +4588,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>schwenkarm sensor links defekt, robtech informiert</t>
+          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>schwenkarm sensor links defekt, robtech informiert</t>
+          <t>schwenkarm (zylinder .sensor einstellen.) robotech an der anlage</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4603,12 +4603,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sensor bauteilerkennung schaltet nicht</t>
+          <t>schwenkarm sensor links defekt, robtech informiert</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>sensor bauteilerkennung schaltet nicht</t>
+          <t>schwenkarm sensor links defekt, robtech informiert</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4618,42 +4618,42 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sensor defekt robotech informiert</t>
+          <t>sensor bauteilerkennung schaltet nicht</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>sensor defekt robotech informiert</t>
+          <t>sensor bauteilerkennung schaltet nicht</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sew antrieb (robtech wurde informiert)</t>
+          <t>sensor defekt robotech informiert</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>sew antrieb (robtech wurde informiert)</t>
+          <t>sensor defekt robotech informiert</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sew antrieb (stw stüße links eingeklemmt)</t>
+          <t>sew antrieb (robtech wurde informiert)</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>sew antrieb (stw stüße links eingeklemmt)</t>
+          <t>sew antrieb (robtech wurde informiert)</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4663,12 +4663,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sew antrieb fehler - robtechnik informiert</t>
+          <t>sew antrieb (stw stüße links eingeklemmt)</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>sew antrieb fehler - robtechnik informiert</t>
+          <t>sew antrieb (stw stüße links eingeklemmt)</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4678,12 +4678,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sew antrieb m3</t>
+          <t>sew antrieb fehler - robtechnik informiert</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>sew antrieb m3</t>
+          <t>sew antrieb fehler - robtechnik informiert</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4693,87 +4693,87 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
+          <t>sew antrieb m3</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
+          <t>sew antrieb m3</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sew antriebs-störung</t>
+          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>sew antriebs-störung</t>
+          <t>sew antrieb op10 m3 ( siehe baustein für fehlercode ), fehlercode : 26,28</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sew antriebsstörung ( fehler 26 )</t>
+          <t>sew antriebs-störung</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>sew antriebsstörung ( fehler 26 )</t>
+          <t>sew antriebs-störung</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sew antriebsstörung 26</t>
+          <t>sew antriebsstörung ( fehler 26 )</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>sew antriebsstörung 26</t>
+          <t>sew antriebsstörung ( fehler 26 )</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
+          <t>sew antriebsstörung 26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
+          <t>sew antriebsstörung 26</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
+          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
+          <t>sew antriebsstörung drehachse ( siehe baustein fehlercode )</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4783,12 +4783,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech an der anlage</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4798,12 +4798,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
+          <t>sew antriebsstörung drehachse, fehlercode 42, robtech informiert</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4813,57 +4813,57 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>sew antriebsstörung, robtech informiert</t>
+          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>sew antriebsstörung, robtech informiert</t>
+          <t>sew antriebsstörung op 120 und 130, robtech informiert</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
+          <t>sew antriebsstörung, robtech informiert</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
+          <t>sew antriebsstörung, robtech informiert</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>softwareendabschalter a6 störung, robtech informiert</t>
+          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>softwareendabschalter a6 störung, robtech informiert</t>
+          <t>sicherheitsverriegelung offen ( pin nicht zurück gefahren )</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>softwarendabschaltungs störung bei op 120.1</t>
+          <t>softwareendabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>softwarendabschaltungs störung bei op 120.1</t>
+          <t>softwareendabschalter a6 störung, robtech informiert</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4873,27 +4873,27 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>softwereendschalter a6. ( robotech an der anlage )</t>
+          <t>softwarendabschaltungs störung bei op 120.1</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>softwereendschalter a6. ( robotech an der anlage )</t>
+          <t>softwarendabschaltungs störung bei op 120.1</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
+          <t>softwereendschalter a6. ( robotech an der anlage )</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
+          <t>softwereendschalter a6. ( robotech an der anlage )</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4903,12 +4903,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
+          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
+          <t>sollgeschwindigkeits probleme bei 883 - 884 stirnwänden mehrfach, kleine stirnwände</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4918,12 +4918,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>spanner klemmt.</t>
+          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>spanner klemmt.</t>
+          <t>sonderbleche 744 - 955 viele ansaugprobleme trotz abkleben</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4933,12 +4933,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>spanner richten (schlosser an der anlage)</t>
+          <t>spanner klemmt.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>spanner richten (schlosser an der anlage)</t>
+          <t>spanner klemmt.</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4948,102 +4948,102 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>spanner störung, robtech informiert</t>
+          <t>spanner richten (schlosser an der anlage)</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>spanner störung, robtech informiert</t>
+          <t>spanner richten (schlosser an der anlage)</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht in op.70</t>
+          <t>spanner störung, robtech informiert</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht in op.70</t>
+          <t>spanner störung, robtech informiert</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
+          <t>spanner- knoten 1 spannen nicht in op.70</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
+          <t>spanner- knoten 1 spannen nicht in op.70</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
+          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
+          <t>spanner- knoten 1 spannen nicht robotech an der anlage</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
+          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
+          <t>spanner- knoten 1 spannen nicht robotech informiert</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
+          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
+          <t>spanner- knoten 3 sensor falsche werte . robotech in der anlage</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken komplettiert</t>
+          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken komplettiert</t>
+          <t>steht zu weit vorne in op 120.2 und r 06 fährt kollision. robtech vor ort</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5053,12 +5053,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
+          <t>stirnwand auf den böcken komplettiert</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
+          <t>stirnwand auf den böcken komplettiert</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5068,22 +5068,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>stirnwand kompletiert</t>
+          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>stirnwand kompletiert</t>
+          <t>stirnwand auf den böcken nachgearbeitet ( stütze gewechselt )</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>stirnwand komplettiert</t>
+          <t>stirnwand kompletiert</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5098,192 +5098,192 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>stirnwand komplettieren</t>
+          <t>stirnwand komplettiert</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>stirnwand komplettieren</t>
+          <t>stirnwand kompletiert</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>stirnwand nacharbeiten.</t>
+          <t>stirnwand komplettieren</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>stirnwand nacharbeiten.</t>
+          <t>stirnwand komplettieren</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>stirnwand nachgearbeitet und komplettiert</t>
+          <t>stirnwand nacharbeiten.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>stirnwand nachgearbeitet und komplettiert</t>
+          <t>stirnwand nacharbeiten.</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>stirnwand von draußen komplettiert</t>
+          <t>stirnwand nachgearbeitet und komplettiert</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>stirnwand von draußen komplettiert</t>
+          <t>stirnwand nachgearbeitet und komplettiert</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>stirnwände komplettiert</t>
+          <t>stirnwand von draußen komplettiert</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>stirnwände komplettiert</t>
+          <t>stirnwand von draußen komplettiert</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>stirnwände nacharbeiten ( schleifen )</t>
+          <t>stirnwände komplettiert</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>stirnwände nacharbeiten ( schleifen )</t>
+          <t>stirnwände komplettiert</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>strom und gasdüse reinigen</t>
+          <t>stirnwände nacharbeiten ( schleifen )</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>strom und gasdüse reinigen</t>
+          <t>stirnwände nacharbeiten ( schleifen )</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>stromdüse fest gebrannt</t>
+          <t>strom und gasdüse reinigen</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>stromdüse fest gebrannt</t>
+          <t>strom und gasdüse reinigen</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>stw er 3 leute helfen aus</t>
+          <t>stromausfall</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>stw er 3 leute helfen aus</t>
+          <t>stromausfall</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stromdüse fest gebrannt</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>nacharbeiten stw</t>
+          <t>stw er 3 leute helfen aus</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>stw nacharbeiten</t>
+          <t>stw er 3 leute helfen aus</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer )</t>
+          <t>nacharbeiten stw</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>stw nacharbeiten (kratzer)</t>
+          <t>stw nacharbeiten</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5293,27 +5293,27 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
+          <t>stw nacharbeiten (kratzer )</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
+          <t>stw nacharbeiten (kratzer)</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5323,72 +5323,72 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet (kratzer)</t>
+          <t>stw nachgearbeitet</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>stw nachgearbeitet (kratzer)</t>
+          <t>stw nachgearbeitet</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>stw rungen eingebaut</t>
+          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>stw rungen eingebaut</t>
+          <t>stw nachgearbeitet ( schweißnaht schlecht ). 953 belche n.i.o</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>stw von draußen komplettiert</t>
+          <t>stw nachgearbeitet (kratzer)</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>stw von draußen komplettiert</t>
+          <t>stw nachgearbeitet (kratzer)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>stw-test robotech an der anlage</t>
+          <t>stw rungen eingebaut</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>stw-test robotech an der anlage</t>
+          <t>stw rungen eingebaut</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
+          <t>stw von draußen komplettiert</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
+          <t>stw von draußen komplettiert</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5398,72 +5398,72 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>stw. mit 5 knoten</t>
+          <t>stw-test robotech an der anlage</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>stw. mit 5 knoten</t>
+          <t>stw-test robotech an der anlage</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>stw.-mit 5 knoten</t>
+          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>stw.-mit 5 knoten</t>
+          <t>stw. eckrungen nachgearbeitet aus. sr.09</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
+          <t>stw. mit 5 knoten</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
+          <t>stw. mit 5 knoten</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
+          <t>stw.-mit 5 knoten</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
+          <t>stw.-mit 5 knoten</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true</t>
+          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true</t>
+          <t>störung ( linearachse fährt nicht ans blech ) robtech informiert</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5473,12 +5473,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
+          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
+          <t>störung ( wait for input knotengreifer 1 l gelöst ) true ( robtech informiert )</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5488,72 +5488,72 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>störung .robotech an der anlage.</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>störung .robotech an der anlage.</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>störung a-6 . robotech informiert.</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>störung a-6 . robotech informiert.</t>
+          <t>störung ( wait for input stw spanner lv_ast ) true (robotech in der anlage )</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>störung abholen knoten 3, robtech informiert</t>
+          <t>störung .robotech an der anlage.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>störung abholen knoten 3, robtech informiert</t>
+          <t>störung .robotech an der anlage.</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>störung bei leoniefahrt, robotertechniker informiert</t>
+          <t>störung a-6 . robotech informiert.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>störung bei leoniefahrt, robotertechniker informiert</t>
+          <t>störung a-6 . robotech informiert.</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
+          <t>störung abholen knoten 3, robtech informiert</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
+          <t>störung abholen knoten 3, robtech informiert</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5563,12 +5563,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>störung beim abholen in op120.1 , robtech informiert</t>
+          <t>störung bei leoniefahrt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>störung beim abholen in op120.1 , robtech informiert</t>
+          <t>störung bei leoniefahrt, robotertechniker informiert</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5578,27 +5578,27 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim abholen aus op.130-1 ( robotech informiert )</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3 in op 70</t>
+          <t>störung beim abholen in op120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>störung beim abholen vom knoten 3 in op 70</t>
+          <t>störung beim abholen in op120.1 , robtech informiert</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5608,42 +5608,42 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>störung beim abholen von blech, robtech informiert</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>störung beim abholen von blech, robtech informiert</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 1 und 3</t>
+          <t>störung beim abholen von knoten 3 in op 70</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 1 und 3</t>
+          <t>störung beim abholen vom knoten 3 in op 70</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3</t>
+          <t>störung beim abholen von blech, robtech informiert</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>störung beim abholen von knoten 3</t>
+          <t>störung beim abholen von blech, robtech informiert</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5653,27 +5653,27 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>störung beim andrücken von stw-mt oben links</t>
+          <t>störung beim abholen von knoten 1 und 3</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>störung beim andrücken von stw-mt oben links</t>
+          <t>störung beim abholen von knoten 1 und 3</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
+          <t>störung beim abholen von knoten 3</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
+          <t>störung beim abholen von knoten 3</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5683,27 +5683,27 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
+          <t>störung beim andrücken von stw-mt oben links</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
+          <t>störung beim andrücken von stw-mt oben links</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
+          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
+          <t>störung beim auflegen von knoten 4-5 robtech informiert</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5713,12 +5713,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 054 -285 )</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5728,12 +5728,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
+          <t>störung beim einlegen vom trapez - blech in die op, robtech informiert ( trapez - bleche 085 - 283 )</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5743,87 +5743,87 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>störung beim knoten abholen in op 70, robtech informiert</t>
+          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>störung beim knoten abholen in op 70, robtech informiert</t>
+          <t>störung beim einlegen von blech in op130.1 ohne meldung, robtech informiert</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
+          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
+          <t>störung beim fördern vom knoten zum endnehmen, robtech informiert</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
+          <t>störung beim knoten abholen in op 70, robtech informiert</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
+          <t>störung beim knoten abholen in op 70, robtech informiert</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>störung beim versuchen zu schweißen</t>
+          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>störung beim versuchen zu schweißen</t>
+          <t>störung beim stütze schwenken nachdem die stw fertig geschweißt ist.</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
+          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
+          <t>störung beim tisch drehen. tisch stand verkehrt und zeigt trotzdem 180 grad an. robtech informiert ( stirnwand aus op50 gefallen )</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>störung drehachse. robotech informiert.</t>
+          <t>störung beim versuchen zu schweißen</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>störung drehachse. robotech informiert.</t>
+          <t>störung beim versuchen zu schweißen</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -5833,42 +5833,42 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>störung durch drahtsehne im brenner, tauschen</t>
+          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>störung durch drahtsehne im brenner, tauschen</t>
+          <t>störung der drehachse der gesamtvorrichtung, robtech informiert</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
+          <t>störung drehachse. robotech informiert.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
+          <t>störung drehachse. robotech informiert.</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
+          <t>störung durch drahtsehne im brenner, tauschen</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
+          <t>störung durch drahtsehne im brenner, tauschen</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5878,42 +5878,42 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
+          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
+          <t>störung nach dem schweißen des 4. knotens ( mehrfach )</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
+          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
+          <t>störung nach dem schweißen von knoten 4 , robtech informiert</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>störung schweißdraht</t>
+          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>störung schweißdraht</t>
+          <t>störung nach fehlerhafter leonie fahrt, ( software endabschalter a6 ) robtech informiert, brenner gewechselt</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -5923,72 +5923,72 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>störung stiftzieher</t>
+          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>störung stiftzieher</t>
+          <t>störung r 06 + r07 beim schweißen in op 130.1, nach störung von op130 / op120, robtech informiert</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall</t>
+          <t>störung schweißdraht</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall</t>
+          <t>störung schweißdraht</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall robo tech. an der anlage.</t>
+          <t>störung stiftzieher</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>störung wegen stromausfall robo tech. an der anlage.</t>
+          <t>störung stiftzieher</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
+          <t>störung wegen stromausfall</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
+          <t>störung wegen stromausfall</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
+          <t>störung wegen stromausfall robo tech. an der anlage.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
+          <t>störung wegen stromausfall robo tech. an der anlage.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -5998,57 +5998,57 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
+          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
+          <t>störung, r. o1 legt bleche nicht ein, obwohl es keine störung angezeigt gibt, robtech informiert</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>störungen beim abholen in op 25, robtech informiert</t>
+          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>störungen beim abholen in op 25, robtech informiert</t>
+          <t>störung, robtech informiert, ( programmpunkt nicht gefunden )</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>stütze andrücken störung</t>
+          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>stütze andrücken störung</t>
+          <t>störung, warten auf input ( lv gst ), robtech informiert</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
+          <t>störungen beim abholen in op 25, robtech informiert</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
+          <t>störungen beim abholen in op 25, robtech informiert</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -6058,27 +6058,27 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
+          <t>stütze andrücken störung</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
+          <t>stütze andrücken störung</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
+          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
+          <t>stütze lösen sich nicht,robotechniker in der anlage</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6088,42 +6088,42 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>tauschbox</t>
+          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>tauschbox</t>
+          <t>stütze schwenken störung nach dem das schweißen abgeschlossen ist</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>tb. verschmutzt (schleifen)</t>
+          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>tb. verschmutzt (schleifen)</t>
+          <t>stützen schweißnähte nachteachen, robtech in der anlage</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
+          <t>tauschbox</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
+          <t>tauschbox</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6133,27 +6133,27 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
+          <t>tb. verschmutzt (schleifen)</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
+          <t>tb. verschmutzt (schleifen)</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>tor sensor nicht geschaltet</t>
+          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>tor sensor nicht geschaltet</t>
+          <t>test fahren ( mt ohne qt oben ), robtech und teamleiter an der anlage</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6163,87 +6163,87 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht</t>
+          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht</t>
+          <t>tor sensor in der anlage richtung heckrunge nicht geschaltet</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht robotech in der anlage</t>
+          <t>tor sensor nicht geschaltet</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>torsensor schaltet nicht robotech in der anlage</t>
+          <t>tor sensor nicht geschaltet</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
+          <t>torsensor schaltet nicht</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
+          <t>torsensor schaltet nicht</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
+          <t>torsensor schaltet nicht robotech in der anlage</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
+          <t>torsensor schaltet nicht robotech in der anlage</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
+          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
+          <t>trapez -blech spanner unten links öffnet nicht richtig</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
+          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
+          <t>trapezbleche auffüllen 054 - 285, warten auf staplerfahrer</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6253,27 +6253,27 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
+          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
+          <t>trapezbleche mit nicht richtig verschweißter mittelnaht in op 120.1 durch roboter in automatikbetrieb eingelegt, robtech informiert</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
+          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
+          <t>turm dreht nicht mehr. fehler sew antrieb. elektriker informiert.</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -6283,12 +6283,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
+          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
+          <t>und op-50 daten nicht verfügbar ( warten auf robotech )</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6298,147 +6298,147 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden</t>
+          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden</t>
+          <t>unerreichbarer punkt ( a.6 ) robotech informiert.</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
+          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
+          <t>unnd r 07 kontaktrohr gewechselt und gasdüse gereinigt</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
+          <t>vakuum nicht vorhanden</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
+          <t>vakuum nicht vorhanden</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
+          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
+          <t>vakuum nicht vorhanden ( bauteil beim anheben in op 25 aus saugern gefallen ), robtech informiert</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
+          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
+          <t>vakuum nicht vorhanden ( bleche 229-230. ölig. )</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
+          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
+          <t>vakuum nicht vorhanden ( bleche kleben aneinander )</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
+          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
+          <t>vakuum nicht vorhanden ( bleche ölig und kleben dadurch aneinander )</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
+          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
+          <t>vakuum nicht vorhanden ( blechhe nass und kleben zusammen )</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
+          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
+          <t>vakuum nicht vorhanden ( dreck auf dem blech )</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei blechen 953</t>
+          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bei blechen 953</t>
+          <t>vakuum nicht vorhanden ( in op-30 ) neue modell -551 blech</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6448,12 +6448,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
+          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
+          <t>vakuum nicht vorhanden bei 230 anheben aus op 25</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6463,57 +6463,57 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op-50</t>
+          <t>vakuum nicht vorhanden bei blechen 953</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op-50</t>
+          <t>vakuum nicht vorhanden bei blechen 953</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op.50</t>
+          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden in op.50</t>
+          <t>vakuum nicht vorhanden bleche kleben aneinander</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
+          <t>vakuum nicht vorhanden in op-50</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
+          <t>vakuum nicht vorhanden in op-50</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>vakuum probleme. robtech informiert</t>
+          <t>vakuum nicht vorhanden in op.50</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>vakuum probleme. robtech informiert</t>
+          <t>vakuum nicht vorhanden in op.50</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6523,27 +6523,27 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht</t>
+          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht</t>
+          <t>vakuum nicht vorhanden, bleche nass und kleben dadurch aneinander</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
+          <t>vakuum probleme. robtech informiert</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
+          <t>vakuum probleme. robtech informiert</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6553,72 +6553,72 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
+          <t>vakuumkreis 1 schaltet nicht</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
+          <t>vakuumkreis 1 schaltet nicht</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-30. )</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op 50</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op 50</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.)</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
+          <t>vakuumkreis 1 schaltet nicht (in op-50.) bei l-4</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
+          <t>vakuumkreis 1 schaltet nicht in op 50</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
+          <t>vakuumkreis 1 schaltet nicht in op 50</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6628,12 +6628,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
+          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
+          <t>vakuumkreis 1 schaltet nicht in op-120-1</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6643,12 +6643,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
+          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
+          <t>vakuumkreis 1 schaltet nicht in op-30 robotech informiert</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6658,27 +6658,27 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht</t>
+          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht</t>
+          <t>vakuumkreis 1 schaltet nicht robotech und schlosser an der anlage</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht in op.50</t>
+          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>vakuumkreis 2 schaltet nicht in op.50</t>
+          <t>vakuumkreis 1 schaltet nicht sauger zieht luft beim abholen in op50 von l4 stirnwand</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6688,27 +6688,27 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>vakuumkreis 3 schaltet nicht</t>
+          <t>vakuumkreis 2 schaltet nicht</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>vakuumkreis 3 schaltet nicht</t>
+          <t>vakuumkreis 2 schaltet nicht</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>vakuumstörung in op 50, robtech in der anlage</t>
+          <t>vakuumkreis 2 schaltet nicht in op.50</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>vakuumstörung in op 50, robtech in der anlage</t>
+          <t>vakuumkreis 2 schaltet nicht in op.50</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6718,27 +6718,27 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
+          <t>vakuumkreis 3 schaltet nicht</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
+          <t>vakuumkreis 3 schaltet nicht</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>warnstreik</t>
+          <t>vakuumstörung in op 50, robtech in der anlage</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>warnstreik</t>
+          <t>vakuumstörung in op 50, robtech in der anlage</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6748,12 +6748,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>warten auf 230 bleche</t>
+          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>warten auf 230 bleche</t>
+          <t>verschlauchung an der banane abgerissen, neu verbinden</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6763,12 +6763,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>warten auf bleche 953</t>
+          <t>warnstreik</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>warten auf bleche 953</t>
+          <t>warnstreik</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6778,12 +6778,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>warten auf coll detected op 130.1</t>
+          <t>warten auf 230 bleche</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>warten auf coll detected op 130.1</t>
+          <t>warten auf 230 bleche</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -6793,27 +6793,27 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>warten auf eckrungen</t>
+          <t>warten auf bleche 953</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>warten auf eckrungen</t>
+          <t>warten auf bleche 953</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
+          <t>warten auf coll detected op 130.1</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
+          <t>warten auf coll detected op 130.1</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -6823,27 +6823,27 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>warten auf robtech</t>
+          <t>warten auf eckrungen</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>warten auf robtech</t>
+          <t>warten auf eckrungen</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>warten auf rungen (nur ein staplerfahrer)</t>
+          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>warten auf rungen (nur ein staplerfahrer)</t>
+          <t>warten auf eckrungen ( gestell falsch gemeldet abklären mit teamleiter )</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -6853,42 +6853,42 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
+          <t>warten auf robtech</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
+          <t>warten auf robtech</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
+          <t>warten auf rungen (nur ein staplerfahrer)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
+          <t>warten auf rungen (nur ein staplerfahrer)</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>warten auf stüzten l5 endnummer 740</t>
+          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>warten auf stüzten l5 endnummer 740</t>
+          <t>warten auf staplerfahrer ( bleche 952 auffüllen )</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6898,192 +6898,192 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
+          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
+          <t>warten auf staplerfahrer zwecks vollen gestellen und trapez bleche tauschen</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>wartung</t>
+          <t>warten auf stüzten l5 endnummer 740</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>wartung</t>
+          <t>warten auf stüzten l5 endnummer 740</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>wartungsplan</t>
+          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>wartungsplan</t>
+          <t>wartet auf stationsfeigabe in op 90 ( robotech an de anlage )</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>794</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>wartungsplan + tauschbox</t>
+          <t>wartung</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>wartungsplan + tauschbox</t>
+          <t>wartung</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>wartungsplan und tauschbox</t>
+          <t>wartungsplan</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>wartungsplan und tauschbox</t>
+          <t>wartungsplan</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>2</v>
+        <v>798</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>wartungsplan.</t>
+          <t>wartungsplan + tauschbox</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>wartungsplan.</t>
+          <t>wartungsplan + tauschbox</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>wartungsplan und tauschbox</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>wartungsplan und tauschbox</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>reinigen und werkzeug einschließen</t>
+          <t>wartungsplan.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigen</t>
+          <t>wartungsplan.</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigung</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>werkzeug einschließen und reinigung</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>werkzeug wegpacken, reinigen</t>
+          <t>reinigen und werkzeug einschließen</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>werkzeug wegpacken, reinigen</t>
+          <t>werkzeug einschließen und reinigen</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
+          <t>werkzeug einschließen und reinigung</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
+          <t>werkzeug einschließen und reinigung</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>wöchentliche reinigung</t>
+          <t>werkzeug wegpacken, reinigen</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>wöchentliche reinigung</t>
+          <t>werkzeug wegpacken, reinigen</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>zwei neue mitarbeiter anlernen</t>
+          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>zwei neue mitarbeiter anlernen</t>
+          <t>wiederhohlt kollisionsabfrage durch roboter 6 und 7</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7093,42 +7093,42 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>zylinder defekt (robotech in der anlage,)</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>zylinder defekt (robotech in der anlage,)</t>
+          <t>wöchentliche reinigung</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>zündfehler</t>
+          <t>zwei neue mitarbeiter anlernen</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>zündfehler</t>
+          <t>zwei neue mitarbeiter anlernen</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>zündfehler &gt;ohne meldung</t>
+          <t>zylinder defekt (robotech in der anlage,)</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>zündfehler &gt;ohne meldung</t>
+          <t>zylinder defekt (robotech in der anlage,)</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7138,30 +7138,60 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
+          <t>zündfehler</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
+          <t>zündfehler &gt;ohne meldung</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>zündfehler &gt;ohne meldung</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>zündfehler. drahtfass leer. bleibt in korrektionsprogram hängen. robtech vor ort</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
           <t>zündfehler. stromdüse fest gebrannt</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>zündfehler. stromdüse fest gebrannt</t>
         </is>
       </c>
-      <c r="C449" t="n">
+      <c r="C451" t="n">
         <v>3</v>
       </c>
     </row>
